--- a/victory_giant/dist/20261025_勝宏科技模型_v0.1.1.xlsx
+++ b/victory_giant/dist/20261025_勝宏科技模型_v0.1.1.xlsx
@@ -6232,7 +6232,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.xlsx</t>
+      <t xml:space="preserve">_v0.3.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -6431,7 +6431,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.xlsx</t>
+      <t xml:space="preserve">_v0.3.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -6552,7 +6552,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.xlsx</t>
+      <t xml:space="preserve">_v0.3.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -6673,7 +6673,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.xlsx</t>
+      <t xml:space="preserve">_v0.3.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -6794,7 +6794,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.xlsx</t>
+      <t xml:space="preserve">_v0.3.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -6915,7 +6915,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.xlsx</t>
+      <t xml:space="preserve">_v0.3.1.xlsx</t>
     </r>
     <r>
       <rPr>

--- a/victory_giant/dist/20261025_勝宏科技模型_v0.1.1.xlsx
+++ b/victory_giant/dist/20261025_勝宏科技模型_v0.1.1.xlsx
@@ -5041,7 +5041,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">markets/network/dist/20261023_AI</t>
+      <t xml:space="preserve">markets/network/dist/20261026_AI</t>
     </r>
     <r>
       <rPr>
@@ -5060,7 +5060,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.2.3.xlsx</t>
     </r>
     <r>
       <rPr>

--- a/victory_giant/dist/20261025_勝宏科技模型_v0.1.1.xlsx
+++ b/victory_giant/dist/20261025_勝宏科技模型_v0.1.1.xlsx
@@ -5354,7 +5354,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">markets/chip_bridge/dist/20261023_</t>
+      <t xml:space="preserve">markets/chip_bridge/dist/20261027_</t>
     </r>
     <r>
       <rPr>
@@ -5373,7 +5373,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.1.xlsx</t>
+      <t xml:space="preserve">_v0.2.2.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -5928,7 +5928,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">markets/chip_bridge/dist/20261023_</t>
+      <t xml:space="preserve">markets/chip_bridge/dist/20261027_</t>
     </r>
     <r>
       <rPr>
@@ -5947,7 +5947,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.1.xlsx</t>
+      <t xml:space="preserve">_v0.2.2.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -42627,7 +42627,7 @@
         <v>32</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="G5" s="7" t="s">
         <v>33</v>
@@ -46214,7 +46214,7 @@
       </c>
       <c r="C12" s="21" t="n">
         <f aca="false">PL!D70*PL!D72</f>
-        <v>10.5297921189288</v>
+        <v>10.5297921189287</v>
       </c>
       <c r="D12" s="21" t="n">
         <f aca="false">PL!E70*PL!E72</f>
@@ -46241,7 +46241,7 @@
       </c>
       <c r="C13" s="16" t="n">
         <f aca="false">PL!D75</f>
-        <v>0.247531793970354</v>
+        <v>0.247531793970355</v>
       </c>
       <c r="D13" s="16" t="n">
         <f aca="false">PL!E75</f>
@@ -46249,7 +46249,7 @@
       </c>
       <c r="E13" s="16" t="n">
         <f aca="false">PL!F75</f>
-        <v>0.198025435176283</v>
+        <v>0.198025435176284</v>
       </c>
       <c r="F13" s="16" t="n">
         <f aca="false">PL!G75</f>
@@ -46272,15 +46272,15 @@
       </c>
       <c r="D14" s="22" t="n">
         <f aca="false">PL!E76/fx</f>
-        <v>6.32760199627351</v>
+        <v>6.32760199627352</v>
       </c>
       <c r="E14" s="22" t="n">
         <f aca="false">PL!F76/fx</f>
-        <v>8.03132395958544</v>
+        <v>8.03132395958545</v>
       </c>
       <c r="F14" s="22" t="n">
         <f aca="false">PL!G76/fx</f>
-        <v>9.20392251340877</v>
+        <v>9.20392251340878</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -46300,11 +46300,11 @@
       </c>
       <c r="E15" s="22" t="n">
         <f aca="false">PL!F81/fx</f>
-        <v>8.03132395958544</v>
+        <v>8.03132395958545</v>
       </c>
       <c r="F15" s="22" t="n">
         <f aca="false">PL!G81/fx</f>
-        <v>9.20392251340877</v>
+        <v>9.20392251340878</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -46316,7 +46316,7 @@
       </c>
       <c r="C16" s="20" t="n">
         <f aca="false">PL!D87</f>
-        <v>111.389307286659</v>
+        <v>111.38930728666</v>
       </c>
       <c r="D16" s="20" t="n">
         <f aca="false">PL!E87</f>
@@ -46328,7 +46328,7 @@
       </c>
       <c r="F16" s="20" t="n">
         <f aca="false">PL!G87</f>
-        <v>153.04519523496</v>
+        <v>153.045195234961</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -46402,11 +46402,11 @@
       </c>
       <c r="E19" s="16" t="n">
         <f aca="false">PL!F86</f>
-        <v>0.986312346288996</v>
+        <v>0.986312346288997</v>
       </c>
       <c r="F19" s="16" t="n">
         <f aca="false">PL!G86</f>
-        <v>0.913580873028148</v>
+        <v>0.913580873028149</v>
       </c>
       <c r="G19" s="3" t="s">
         <v>472</v>
@@ -46421,7 +46421,7 @@
       </c>
       <c r="C20" s="21" t="n">
         <f aca="false">PL!D70*PL!D72-PL!D81/fx</f>
-        <v>7.92333378559543</v>
+        <v>7.92333378559542</v>
       </c>
       <c r="D20" s="21" t="n">
         <f aca="false">PL!E70*PL!E72-PL!E81/fx</f>
@@ -46540,11 +46540,11 @@
       </c>
       <c r="F5" s="21" t="n">
         <f aca="false">F83</f>
-        <v>64.5810970084141</v>
+        <v>64.5810970084142</v>
       </c>
       <c r="G5" s="21" t="n">
         <f aca="false">G83</f>
-        <v>72.4609592901069</v>
+        <v>72.460959290107</v>
       </c>
       <c r="H5" s="23" t="n">
         <f aca="false">H83</f>
@@ -46552,11 +46552,11 @@
       </c>
       <c r="I5" s="23" t="n">
         <f aca="false">I83</f>
-        <v>86.2423476187718</v>
+        <v>86.2423476187719</v>
       </c>
       <c r="J5" s="23" t="n">
         <f aca="false">J83</f>
-        <v>91.4168884758982</v>
+        <v>91.4168884758983</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -46576,7 +46576,7 @@
       </c>
       <c r="F6" s="16" t="n">
         <f aca="false">F84</f>
-        <v>0.350667730682813</v>
+        <v>0.350667730682815</v>
       </c>
       <c r="G6" s="16" t="n">
         <f aca="false">G84</f>
@@ -46616,11 +46616,11 @@
       </c>
       <c r="F7" s="21" t="n">
         <f aca="false">F81</f>
-        <v>53.9704970084141</v>
+        <v>53.9704970084142</v>
       </c>
       <c r="G7" s="21" t="n">
         <f aca="false">G81</f>
-        <v>61.8503592901069</v>
+        <v>61.850359290107</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -46668,11 +46668,11 @@
       </c>
       <c r="F9" s="16" t="n">
         <f aca="false">F86</f>
-        <v>0.986312346288996</v>
+        <v>0.986312346288997</v>
       </c>
       <c r="G9" s="16" t="n">
         <f aca="false">G86</f>
-        <v>0.913580873028148</v>
+        <v>0.913580873028149</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -46768,7 +46768,7 @@
       </c>
       <c r="J12" s="23" t="n">
         <f aca="false">J98</f>
-        <v>24.4489205143475</v>
+        <v>24.4489205143476</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -46868,7 +46868,7 @@
       </c>
       <c r="F15" s="16" t="n">
         <f aca="false">F102</f>
-        <v>0.388349461531279</v>
+        <v>0.38834946153128</v>
       </c>
       <c r="G15" s="16" t="n">
         <f aca="false">G102</f>
@@ -46880,11 +46880,11 @@
       </c>
       <c r="I15" s="24" t="n">
         <f aca="false">I102</f>
-        <v>0.0806716652741595</v>
+        <v>0.0806716652741597</v>
       </c>
       <c r="J15" s="24" t="n">
         <f aca="false">J102</f>
-        <v>0.0600000000000001</v>
+        <v>0.0599999999999998</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -46913,23 +46913,23 @@
       </c>
       <c r="F18" s="21" t="n">
         <f aca="false">F129</f>
-        <v>53.7869976067313</v>
+        <v>53.7869976067314</v>
       </c>
       <c r="G18" s="21" t="n">
         <f aca="false">G129</f>
-        <v>63.1834053965909</v>
+        <v>63.183405396591</v>
       </c>
       <c r="H18" s="23" t="n">
         <f aca="false">H129</f>
-        <v>71.3844699115163</v>
+        <v>71.3844699115164</v>
       </c>
       <c r="I18" s="23" t="n">
         <f aca="false">I129</f>
-        <v>77.4449314706761</v>
+        <v>77.4449314706762</v>
       </c>
       <c r="J18" s="23" t="n">
         <f aca="false">J129</f>
-        <v>80.5427287295032</v>
+        <v>80.5427287295033</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -46949,7 +46949,7 @@
       </c>
       <c r="F19" s="16" t="n">
         <f aca="false">F130</f>
-        <v>0.124916815647471</v>
+        <v>0.124916815647473</v>
       </c>
       <c r="G19" s="16" t="n">
         <f aca="false">G130</f>
@@ -46989,11 +46989,11 @@
       </c>
       <c r="F20" s="21" t="n">
         <f aca="false">F127</f>
-        <v>43.1763976067313</v>
+        <v>43.1763976067314</v>
       </c>
       <c r="G20" s="21" t="n">
         <f aca="false">G127</f>
-        <v>52.5728053965909</v>
+        <v>52.572805396591</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -47045,7 +47045,7 @@
       </c>
       <c r="G22" s="16" t="n">
         <f aca="false">G132</f>
-        <v>0.796610357199478</v>
+        <v>0.796610357199479</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -47133,7 +47133,7 @@
       </c>
       <c r="H25" s="23" t="n">
         <f aca="false">H144</f>
-        <v>17.0481196335342</v>
+        <v>17.0481196335343</v>
       </c>
       <c r="I25" s="23" t="n">
         <f aca="false">I144</f>
@@ -47141,7 +47141,7 @@
       </c>
       <c r="J25" s="23" t="n">
         <f aca="false">J144</f>
-        <v>15.419419465724</v>
+        <v>15.4194194657241</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -47241,7 +47241,7 @@
       </c>
       <c r="F28" s="16" t="n">
         <f aca="false">F148</f>
-        <v>0.123579956841374</v>
+        <v>0.123579956841375</v>
       </c>
       <c r="G28" s="16" t="n">
         <f aca="false">G148</f>
@@ -47253,11 +47253,11 @@
       </c>
       <c r="I28" s="24" t="n">
         <f aca="false">I148</f>
-        <v>-0.0227118448511893</v>
+        <v>-0.0227118448511895</v>
       </c>
       <c r="J28" s="24" t="n">
         <f aca="false">J148</f>
-        <v>-0.0745160242285117</v>
+        <v>-0.0745160242285116</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -47294,7 +47294,7 @@
       </c>
       <c r="H31" s="23" t="n">
         <f aca="false">H175</f>
-        <v>51.5375177854336</v>
+        <v>51.5375177854337</v>
       </c>
       <c r="I31" s="23" t="n">
         <f aca="false">I175</f>
@@ -47302,7 +47302,7 @@
       </c>
       <c r="J31" s="23" t="n">
         <f aca="false">J175</f>
-        <v>55.1961511186778</v>
+        <v>55.1961511186779</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -47322,7 +47322,7 @@
       </c>
       <c r="F32" s="16" t="n">
         <f aca="false">F176</f>
-        <v>-0.10083409938787</v>
+        <v>-0.100834099387869</v>
       </c>
       <c r="G32" s="16" t="n">
         <f aca="false">G176</f>
@@ -47414,7 +47414,7 @@
       </c>
       <c r="F35" s="16" t="n">
         <f aca="false">F178</f>
-        <v>0.656607401649751</v>
+        <v>0.656607401649752</v>
       </c>
       <c r="G35" s="16" t="n">
         <f aca="false">G178</f>
@@ -47474,7 +47474,7 @@
       </c>
       <c r="G37" s="16" t="n">
         <f aca="false">G188</f>
-        <v>0.289085400311093</v>
+        <v>0.289085400311094</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -47510,11 +47510,11 @@
       </c>
       <c r="I38" s="23" t="n">
         <f aca="false">I190</f>
-        <v>8.79819174083814</v>
+        <v>8.79819174083815</v>
       </c>
       <c r="J38" s="23" t="n">
         <f aca="false">J190</f>
-        <v>6.6444146568961</v>
+        <v>6.64441465689611</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -47578,7 +47578,7 @@
       </c>
       <c r="F40" s="17" t="n">
         <f aca="false">F193</f>
-        <v>10.8614617105726</v>
+        <v>10.8614617105727</v>
       </c>
       <c r="G40" s="17" t="n">
         <f aca="false">G193</f>
@@ -47590,11 +47590,11 @@
       </c>
       <c r="I40" s="25" t="n">
         <f aca="false">I193</f>
-        <v>8.95636107746619</v>
+        <v>8.9563610774662</v>
       </c>
       <c r="J40" s="25" t="n">
         <f aca="false">J193</f>
-        <v>6.7638645040374</v>
+        <v>6.76386450403741</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -47614,7 +47614,7 @@
       </c>
       <c r="F41" s="16" t="n">
         <f aca="false">F194</f>
-        <v>-0.152010367906736</v>
+        <v>-0.152010367906735</v>
       </c>
       <c r="G41" s="16" t="n">
         <f aca="false">G194</f>
@@ -47728,7 +47728,7 @@
       </c>
       <c r="D63" s="22" t="n">
         <f aca="false">itc_26*1</f>
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="E63" s="22" t="n">
         <f aca="false">itc_27*1*1</f>
@@ -47896,7 +47896,7 @@
       </c>
       <c r="D70" s="22" t="n">
         <f aca="false">D65*D69/1000</f>
-        <v>10.5297921189288</v>
+        <v>10.5297921189287</v>
       </c>
       <c r="E70" s="22" t="n">
         <f aca="false">E65*E69/1000</f>
@@ -47920,7 +47920,7 @@
       </c>
       <c r="D71" s="21" t="n">
         <f aca="false">D70*fx</f>
-        <v>70.7602030392013</v>
+        <v>70.7602030392012</v>
       </c>
       <c r="E71" s="21" t="n">
         <f aca="false">E70*fx</f>
@@ -47968,7 +47968,7 @@
       </c>
       <c r="D73" s="16" t="n">
         <f aca="false">a26_ai/D71</f>
-        <v>0.247531793970354</v>
+        <v>0.247531793970355</v>
       </c>
       <c r="K73" s="7" t="s">
         <v>510</v>
@@ -48007,7 +48007,7 @@
       </c>
       <c r="D75" s="16" t="n">
         <f aca="false">$D$73*D74</f>
-        <v>0.247531793970354</v>
+        <v>0.247531793970355</v>
       </c>
       <c r="E75" s="16" t="n">
         <f aca="false">$D$73*E74</f>
@@ -48015,7 +48015,7 @@
       </c>
       <c r="F75" s="16" t="n">
         <f aca="false">$D$73*F74</f>
-        <v>0.198025435176283</v>
+        <v>0.198025435176284</v>
       </c>
       <c r="G75" s="16" t="n">
         <f aca="false">$D$73*G74</f>
@@ -48035,15 +48035,15 @@
       </c>
       <c r="E76" s="21" t="n">
         <f aca="false">E71*E75*E72</f>
-        <v>42.521485414958</v>
+        <v>42.5214854149581</v>
       </c>
       <c r="F76" s="21" t="n">
         <f aca="false">F71*F75*F72</f>
-        <v>53.9704970084141</v>
+        <v>53.9704970084142</v>
       </c>
       <c r="G76" s="21" t="n">
         <f aca="false">G71*G75*G72</f>
-        <v>61.8503592901069</v>
+        <v>61.850359290107</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -48151,11 +48151,11 @@
       </c>
       <c r="F81" s="21" t="n">
         <f aca="false">MIN(F76,F79-F80)</f>
-        <v>53.9704970084141</v>
+        <v>53.9704970084142</v>
       </c>
       <c r="G81" s="21" t="n">
         <f aca="false">MIN(G76,G79-G80)</f>
-        <v>61.8503592901069</v>
+        <v>61.850359290107</v>
       </c>
       <c r="K81" s="3" t="s">
         <v>519</v>
@@ -48199,11 +48199,11 @@
       </c>
       <c r="F83" s="21" t="n">
         <f aca="false">F81+F80</f>
-        <v>64.5810970084141</v>
+        <v>64.5810970084142</v>
       </c>
       <c r="G83" s="21" t="n">
         <f aca="false">G81+G80</f>
-        <v>72.4609592901069</v>
+        <v>72.460959290107</v>
       </c>
       <c r="H83" s="23" t="n">
         <f aca="false">G83*(1+H84)</f>
@@ -48211,11 +48211,11 @@
       </c>
       <c r="I83" s="23" t="n">
         <f aca="false">H83*(1+I84)</f>
-        <v>86.2423476187718</v>
+        <v>86.2423476187719</v>
       </c>
       <c r="J83" s="23" t="n">
         <f aca="false">I83*(1+J84)</f>
-        <v>91.4168884758982</v>
+        <v>91.4168884758983</v>
       </c>
       <c r="K83" s="7" t="s">
         <v>521</v>
@@ -48238,7 +48238,7 @@
       </c>
       <c r="F84" s="16" t="n">
         <f aca="false">F83/E83-1</f>
-        <v>0.350667730682813</v>
+        <v>0.350667730682815</v>
       </c>
       <c r="G84" s="16" t="n">
         <f aca="false">G83/F83-1</f>
@@ -48302,11 +48302,11 @@
       </c>
       <c r="F86" s="16" t="n">
         <f aca="false">(F76+F80)/F79</f>
-        <v>0.986312346288996</v>
+        <v>0.986312346288997</v>
       </c>
       <c r="G86" s="16" t="n">
         <f aca="false">(G76+G80)/G79</f>
-        <v>0.913580873028148</v>
+        <v>0.913580873028149</v>
       </c>
       <c r="K86" s="3" t="s">
         <v>525</v>
@@ -48321,7 +48321,7 @@
       </c>
       <c r="D87" s="20" t="n">
         <f aca="false">D81/fx/D65*1000</f>
-        <v>111.389307286659</v>
+        <v>111.38930728666</v>
       </c>
       <c r="E87" s="20" t="n">
         <f aca="false">E81/fx/E65*1000</f>
@@ -48333,7 +48333,7 @@
       </c>
       <c r="G87" s="20" t="n">
         <f aca="false">G81/fx/G65*1000</f>
-        <v>153.04519523496</v>
+        <v>153.045195234961</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -48614,7 +48614,7 @@
       </c>
       <c r="J98" s="23" t="n">
         <f aca="false">J83*J103</f>
-        <v>24.4489205143475</v>
+        <v>24.4489205143476</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -48745,7 +48745,7 @@
       </c>
       <c r="F102" s="16" t="n">
         <f aca="false">F101/E101-1</f>
-        <v>0.388349461531279</v>
+        <v>0.38834946153128</v>
       </c>
       <c r="G102" s="16" t="n">
         <f aca="false">G101/F101-1</f>
@@ -48757,11 +48757,11 @@
       </c>
       <c r="I102" s="24" t="n">
         <f aca="false">I101/H101-1</f>
-        <v>0.0806716652741595</v>
+        <v>0.0806716652741597</v>
       </c>
       <c r="J102" s="24" t="n">
         <f aca="false">J101/I101-1</f>
-        <v>0.0600000000000001</v>
+        <v>0.0599999999999998</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -48858,7 +48858,7 @@
       </c>
       <c r="D109" s="22" t="n">
         <f aca="false">itc_26*1</f>
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="E109" s="22" t="n">
         <f aca="false">itc_27*1*1</f>
@@ -49026,7 +49026,7 @@
       </c>
       <c r="D116" s="22" t="n">
         <f aca="false">D111*D115/1000</f>
-        <v>10.5297921189288</v>
+        <v>10.5297921189287</v>
       </c>
       <c r="E116" s="22" t="n">
         <f aca="false">E111*E115/1000</f>
@@ -49050,7 +49050,7 @@
       </c>
       <c r="D117" s="21" t="n">
         <f aca="false">D116*fx</f>
-        <v>70.7602030392013</v>
+        <v>70.7602030392012</v>
       </c>
       <c r="E117" s="21" t="n">
         <f aca="false">E116*fx</f>
@@ -49098,7 +49098,7 @@
       </c>
       <c r="D119" s="16" t="n">
         <f aca="false">a26_ai/D117</f>
-        <v>0.247531793970354</v>
+        <v>0.247531793970355</v>
       </c>
       <c r="K119" s="7" t="s">
         <v>510</v>
@@ -49137,7 +49137,7 @@
       </c>
       <c r="D121" s="16" t="n">
         <f aca="false">$D$119*D120</f>
-        <v>0.247531793970354</v>
+        <v>0.247531793970355</v>
       </c>
       <c r="E121" s="16" t="n">
         <f aca="false">$D$119*E120</f>
@@ -49145,7 +49145,7 @@
       </c>
       <c r="F121" s="16" t="n">
         <f aca="false">$D$119*F120</f>
-        <v>0.198025435176283</v>
+        <v>0.198025435176284</v>
       </c>
       <c r="G121" s="16" t="n">
         <f aca="false">$D$119*G120</f>
@@ -49165,15 +49165,15 @@
       </c>
       <c r="E122" s="21" t="n">
         <f aca="false">E117*E121*E118</f>
-        <v>42.521485414958</v>
+        <v>42.5214854149581</v>
       </c>
       <c r="F122" s="21" t="n">
         <f aca="false">F117*F121*F118</f>
-        <v>43.1763976067313</v>
+        <v>43.1763976067314</v>
       </c>
       <c r="G122" s="21" t="n">
         <f aca="false">G117*G121*G118</f>
-        <v>52.5728053965909</v>
+        <v>52.572805396591</v>
       </c>
     </row>
     <row r="123" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -49281,11 +49281,11 @@
       </c>
       <c r="F127" s="21" t="n">
         <f aca="false">MIN(F122,F125-F126)</f>
-        <v>43.1763976067313</v>
+        <v>43.1763976067314</v>
       </c>
       <c r="G127" s="21" t="n">
         <f aca="false">MIN(G122,G125-G126)</f>
-        <v>52.5728053965909</v>
+        <v>52.572805396591</v>
       </c>
       <c r="K127" s="3" t="s">
         <v>519</v>
@@ -49329,23 +49329,23 @@
       </c>
       <c r="F129" s="21" t="n">
         <f aca="false">F127+F126</f>
-        <v>53.7869976067313</v>
+        <v>53.7869976067314</v>
       </c>
       <c r="G129" s="21" t="n">
         <f aca="false">G127+G126</f>
-        <v>63.1834053965909</v>
+        <v>63.183405396591</v>
       </c>
       <c r="H129" s="23" t="n">
         <f aca="false">G129*(1+H130)</f>
-        <v>71.3844699115163</v>
+        <v>71.3844699115164</v>
       </c>
       <c r="I129" s="23" t="n">
         <f aca="false">H129*(1+I130)</f>
-        <v>77.4449314706761</v>
+        <v>77.4449314706762</v>
       </c>
       <c r="J129" s="23" t="n">
         <f aca="false">I129*(1+J130)</f>
-        <v>80.5427287295032</v>
+        <v>80.5427287295033</v>
       </c>
       <c r="K129" s="7" t="s">
         <v>521</v>
@@ -49368,7 +49368,7 @@
       </c>
       <c r="F130" s="16" t="n">
         <f aca="false">F129/E129-1</f>
-        <v>0.124916815647471</v>
+        <v>0.124916815647473</v>
       </c>
       <c r="G130" s="16" t="n">
         <f aca="false">G129/F129-1</f>
@@ -49436,7 +49436,7 @@
       </c>
       <c r="G132" s="16" t="n">
         <f aca="false">(G122+G126)/G125</f>
-        <v>0.796610357199478</v>
+        <v>0.796610357199479</v>
       </c>
       <c r="K132" s="3" t="s">
         <v>525</v>
@@ -49451,7 +49451,7 @@
       </c>
       <c r="D133" s="20" t="n">
         <f aca="false">D127/fx/D111*1000</f>
-        <v>111.389307286659</v>
+        <v>111.38930728666</v>
       </c>
       <c r="E133" s="20" t="n">
         <f aca="false">E127/fx/E111*1000</f>
@@ -49463,7 +49463,7 @@
       </c>
       <c r="G133" s="20" t="n">
         <f aca="false">G127/fx/G111*1000</f>
-        <v>153.04519523496</v>
+        <v>153.045195234961</v>
       </c>
     </row>
     <row r="134" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -49653,7 +49653,7 @@
       </c>
       <c r="G141" s="21" t="n">
         <f aca="false">G137-G140</f>
-        <v>19.3306313224847</v>
+        <v>19.3306313224848</v>
       </c>
     </row>
     <row r="142" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -49736,7 +49736,7 @@
       </c>
       <c r="H144" s="23" t="n">
         <f aca="false">H129*H149</f>
-        <v>17.0481196335342</v>
+        <v>17.0481196335343</v>
       </c>
       <c r="I144" s="23" t="n">
         <f aca="false">I129*I149</f>
@@ -49744,7 +49744,7 @@
       </c>
       <c r="J144" s="23" t="n">
         <f aca="false">J129*J149</f>
-        <v>15.419419465724</v>
+        <v>15.4194194657241</v>
       </c>
     </row>
     <row r="145" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -49875,7 +49875,7 @@
       </c>
       <c r="F148" s="16" t="n">
         <f aca="false">F147/E147-1</f>
-        <v>0.123579956841374</v>
+        <v>0.123579956841375</v>
       </c>
       <c r="G148" s="16" t="n">
         <f aca="false">G147/F147-1</f>
@@ -49887,11 +49887,11 @@
       </c>
       <c r="I148" s="24" t="n">
         <f aca="false">I147/H147-1</f>
-        <v>-0.0227118448511893</v>
+        <v>-0.0227118448511895</v>
       </c>
       <c r="J148" s="24" t="n">
         <f aca="false">J147/I147-1</f>
-        <v>-0.0745160242285117</v>
+        <v>-0.0745160242285116</v>
       </c>
     </row>
     <row r="149" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -49988,7 +49988,7 @@
       </c>
       <c r="D155" s="22" t="n">
         <f aca="false">itc_26*1</f>
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="E155" s="22" t="n">
         <f aca="false">itc_27*1*1</f>
@@ -50156,7 +50156,7 @@
       </c>
       <c r="D162" s="22" t="n">
         <f aca="false">D157*D161/1000</f>
-        <v>10.5297921189288</v>
+        <v>10.5297921189287</v>
       </c>
       <c r="E162" s="22" t="n">
         <f aca="false">E157*E161/1000</f>
@@ -50180,7 +50180,7 @@
       </c>
       <c r="D163" s="21" t="n">
         <f aca="false">D162*fx</f>
-        <v>70.7602030392013</v>
+        <v>70.7602030392012</v>
       </c>
       <c r="E163" s="21" t="n">
         <f aca="false">E162*fx</f>
@@ -50228,7 +50228,7 @@
       </c>
       <c r="D165" s="16" t="n">
         <f aca="false">a26_ai/D163</f>
-        <v>0.247531793970354</v>
+        <v>0.247531793970355</v>
       </c>
       <c r="K165" s="7" t="s">
         <v>510</v>
@@ -50267,7 +50267,7 @@
       </c>
       <c r="D167" s="16" t="n">
         <f aca="false">$D$165*D166</f>
-        <v>0.247531793970354</v>
+        <v>0.247531793970355</v>
       </c>
       <c r="E167" s="16" t="n">
         <f aca="false">$D$165*E166</f>
@@ -50275,7 +50275,7 @@
       </c>
       <c r="F167" s="16" t="n">
         <f aca="false">$D$165*F166</f>
-        <v>0.198025435176283</v>
+        <v>0.198025435176284</v>
       </c>
       <c r="G167" s="16" t="n">
         <f aca="false">$D$165*G166</f>
@@ -50295,7 +50295,7 @@
       </c>
       <c r="E168" s="21" t="n">
         <f aca="false">E163*E167*E164</f>
-        <v>42.521485414958</v>
+        <v>42.5214854149581</v>
       </c>
       <c r="F168" s="21" t="n">
         <f aca="false">F163*F167*F164</f>
@@ -50467,7 +50467,7 @@
       </c>
       <c r="H175" s="23" t="n">
         <f aca="false">G175*(1+H176)</f>
-        <v>51.5375177854336</v>
+        <v>51.5375177854337</v>
       </c>
       <c r="I175" s="23" t="n">
         <f aca="false">H175*(1+I176)</f>
@@ -50475,7 +50475,7 @@
       </c>
       <c r="J175" s="23" t="n">
         <f aca="false">I175*(1+J176)</f>
-        <v>55.1961511186778</v>
+        <v>55.1961511186779</v>
       </c>
       <c r="K175" s="7" t="s">
         <v>521</v>
@@ -50498,7 +50498,7 @@
       </c>
       <c r="F176" s="16" t="n">
         <f aca="false">F175/E175-1</f>
-        <v>-0.10083409938787</v>
+        <v>-0.100834099387869</v>
       </c>
       <c r="G176" s="16" t="n">
         <f aca="false">G175/F175-1</f>
@@ -50542,7 +50542,7 @@
       </c>
       <c r="G177" s="16" t="n">
         <f aca="false">G173/G175</f>
-        <v>0.777652584676973</v>
+        <v>0.777652584676974</v>
       </c>
     </row>
     <row r="178" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -50562,7 +50562,7 @@
       </c>
       <c r="F178" s="16" t="n">
         <f aca="false">(F168+F172)/F171</f>
-        <v>0.656607401649751</v>
+        <v>0.656607401649752</v>
       </c>
       <c r="G178" s="16" t="n">
         <f aca="false">(G168+G172)/G171</f>
@@ -50581,7 +50581,7 @@
       </c>
       <c r="D179" s="20" t="n">
         <f aca="false">D173/fx/D157*1000</f>
-        <v>111.389307286659</v>
+        <v>111.38930728666</v>
       </c>
       <c r="E179" s="20" t="n">
         <f aca="false">E173/fx/E157*1000</f>
@@ -50593,7 +50593,7 @@
       </c>
       <c r="G179" s="20" t="n">
         <f aca="false">G173/fx/G157*1000</f>
-        <v>153.04519523496</v>
+        <v>153.045195234961</v>
       </c>
     </row>
     <row r="180" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -50664,7 +50664,7 @@
       </c>
       <c r="F183" s="21" t="n">
         <f aca="false">F173*F182+F172*$D$181</f>
-        <v>15.1020245195662</v>
+        <v>15.1020245195663</v>
       </c>
       <c r="G183" s="21" t="n">
         <f aca="false">G173*G182+G172*$D$181</f>
@@ -50779,7 +50779,7 @@
       </c>
       <c r="F187" s="21" t="n">
         <f aca="false">F183-F186</f>
-        <v>12.5063994195662</v>
+        <v>12.5063994195663</v>
       </c>
       <c r="G187" s="21" t="n">
         <f aca="false">G183-G186</f>
@@ -50811,7 +50811,7 @@
       </c>
       <c r="G188" s="16" t="n">
         <f aca="false">G187/G175</f>
-        <v>0.289085400311093</v>
+        <v>0.289085400311094</v>
       </c>
     </row>
     <row r="189" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -50870,11 +50870,11 @@
       </c>
       <c r="I190" s="23" t="n">
         <f aca="false">I175*I195</f>
-        <v>8.79819174083814</v>
+        <v>8.79819174083815</v>
       </c>
       <c r="J190" s="23" t="n">
         <f aca="false">J175*J195</f>
-        <v>6.6444146568961</v>
+        <v>6.64441465689611</v>
       </c>
     </row>
     <row r="191" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -50969,7 +50969,7 @@
       </c>
       <c r="F193" s="22" t="n">
         <f aca="false">F190/F192</f>
-        <v>10.8614617105726</v>
+        <v>10.8614617105727</v>
       </c>
       <c r="G193" s="22" t="n">
         <f aca="false">G190/G192</f>
@@ -50981,11 +50981,11 @@
       </c>
       <c r="I193" s="28" t="n">
         <f aca="false">I190/I192</f>
-        <v>8.95636107746619</v>
+        <v>8.9563610774662</v>
       </c>
       <c r="J193" s="28" t="n">
         <f aca="false">J190/J192</f>
-        <v>6.7638645040374</v>
+        <v>6.76386450403741</v>
       </c>
     </row>
     <row r="194" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -51005,7 +51005,7 @@
       </c>
       <c r="F194" s="16" t="n">
         <f aca="false">F193/E193-1</f>
-        <v>-0.152010367906736</v>
+        <v>-0.152010367906735</v>
       </c>
       <c r="G194" s="16" t="n">
         <f aca="false">G193/F193-1</f>
@@ -51163,7 +51163,7 @@
       </c>
       <c r="D9" s="17" t="n">
         <f aca="false">PL!F40</f>
-        <v>10.8614617105726</v>
+        <v>10.8614617105727</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -51214,7 +51214,7 @@
       </c>
       <c r="D12" s="17" t="n">
         <f aca="false">PL!I40</f>
-        <v>8.95636107746619</v>
+        <v>8.9563610774662</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -51231,7 +51231,7 @@
       </c>
       <c r="D13" s="17" t="n">
         <f aca="false">PL!J40</f>
-        <v>6.7638645040374</v>
+        <v>6.76386450403741</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -51274,15 +51274,15 @@
       </c>
       <c r="B17" s="17" t="n">
         <f aca="false">B9*(1-$B$15)</f>
-        <v>14.1572387390094</v>
+        <v>14.1572387390095</v>
       </c>
       <c r="C17" s="17" t="n">
         <f aca="false">C9*(1-$B$15)</f>
-        <v>11.4573384670923</v>
+        <v>11.4573384670924</v>
       </c>
       <c r="D17" s="17" t="n">
         <f aca="false">D9*(1-$B$15)</f>
-        <v>8.64709642809096</v>
+        <v>8.64709642809097</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -51299,7 +51299,7 @@
       </c>
       <c r="D18" s="17" t="n">
         <f aca="false">D10*(1-$B$15)</f>
-        <v>9.55280692437027</v>
+        <v>9.55280692437028</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -51312,11 +51312,11 @@
       </c>
       <c r="C19" s="17" t="n">
         <f aca="false">C11*(1-$B$15)</f>
-        <v>13.8164567648881</v>
+        <v>13.8164567648882</v>
       </c>
       <c r="D19" s="17" t="n">
         <f aca="false">D11*(1-$B$15)</f>
-        <v>8.55387841453463</v>
+        <v>8.55387841453464</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -51329,7 +51329,7 @@
       </c>
       <c r="C20" s="17" t="n">
         <f aca="false">C12*(1-$B$15)</f>
-        <v>13.5026595424508</v>
+        <v>13.5026595424509</v>
       </c>
       <c r="D20" s="17" t="n">
         <f aca="false">D12*(1-$B$15)</f>
@@ -51367,7 +51367,7 @@
       </c>
       <c r="D22" s="17" t="n">
         <f aca="false">SUMPRODUCT(D16:D21,1/(1+tp_r)^{1;2;3;4;5;6})+D21*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^6</f>
-        <v>89.5900731303425</v>
+        <v>89.5900731303426</v>
       </c>
       <c r="E22" s="7" t="s">
         <v>560</v>
@@ -51379,7 +51379,7 @@
       </c>
       <c r="B23" s="17" t="n">
         <f aca="false">B22*(1+tp_r)</f>
-        <v>287.368336896726</v>
+        <v>287.368336896727</v>
       </c>
       <c r="C23" s="17" t="n">
         <f aca="false">C22*(1+tp_r)</f>
@@ -51542,7 +51542,7 @@
       </c>
       <c r="B35" s="29" t="n">
         <f aca="false">B33*B34</f>
-        <v>442.977340230993</v>
+        <v>442.977340230994</v>
       </c>
       <c r="E35" s="3" t="s">
         <v>589</v>
@@ -51572,7 +51572,7 @@
       </c>
       <c r="B39" s="29" t="n">
         <f aca="false">tp_w_dcf*B24+(1-tp_w_dcf)*B35</f>
-        <v>322.84375955125</v>
+        <v>322.843759551251</v>
       </c>
       <c r="E39" s="7" t="s">
         <v>593</v>
@@ -51584,7 +51584,7 @@
       </c>
       <c r="B40" s="17" t="n">
         <f aca="false">B35</f>
-        <v>442.977340230993</v>
+        <v>442.977340230994</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -51605,7 +51605,7 @@
       </c>
       <c r="B42" s="16" t="n">
         <f aca="false">B39/px-1</f>
-        <v>0.759558314537008</v>
+        <v>0.75955831453701</v>
       </c>
       <c r="E42" s="3" t="s">
         <v>598</v>
@@ -51626,7 +51626,7 @@
       </c>
       <c r="B44" s="16" t="n">
         <f aca="false">B34/cons_feps-1</f>
-        <v>0.163635579303177</v>
+        <v>0.163635579303179</v>
       </c>
       <c r="E44" s="3" t="s">
         <v>601</v>
@@ -51779,7 +51779,7 @@
       </c>
       <c r="B57" s="19" t="n">
         <f aca="false">px/PL!G14</f>
-        <v>9.30064841451599</v>
+        <v>9.30064841451598</v>
       </c>
       <c r="C57" s="19" t="n">
         <f aca="false">px/PL!G27</f>
@@ -52087,7 +52087,7 @@
       </c>
       <c r="B78" s="19" t="n">
         <f aca="false">px*A78/PL!F14</f>
-        <v>11.3497131997664</v>
+        <v>11.3497131997663</v>
       </c>
       <c r="C78" s="19" t="n">
         <f aca="false">px*A78/PL!F27</f>
@@ -52154,11 +52154,11 @@
       </c>
       <c r="C81" s="19" t="n">
         <f aca="false">px*A81/PL!F27</f>
-        <v>25.4986395995552</v>
+        <v>25.4986395995551</v>
       </c>
       <c r="D81" s="19" t="n">
         <f aca="false">px*A81/PL!F40</f>
-        <v>33.7855078605855</v>
+        <v>33.7855078605854</v>
       </c>
       <c r="E81" s="19" t="n">
         <f aca="false">pe_mid</f>
@@ -52937,19 +52937,19 @@
       </c>
       <c r="C13" s="21" t="n">
         <f aca="false">PL!F83</f>
-        <v>64.5810970084141</v>
+        <v>64.5810970084142</v>
       </c>
       <c r="D13" s="16" t="n">
         <f aca="false">C13/B13-1</f>
-        <v>-0.132382655895558</v>
+        <v>-0.132382655895557</v>
       </c>
       <c r="E13" s="21" t="n">
         <f aca="false">PL!F129</f>
-        <v>53.7869976067313</v>
+        <v>53.7869976067314</v>
       </c>
       <c r="F13" s="16" t="n">
         <f aca="false">E13/B13-1</f>
-        <v>-0.27739641826115</v>
+        <v>-0.277396418261149</v>
       </c>
       <c r="G13" s="21" t="n">
         <f aca="false">PL!F175</f>
@@ -52957,7 +52957,7 @@
       </c>
       <c r="H13" s="16" t="n">
         <f aca="false">G13/B13-1</f>
-        <v>-0.422410180626742</v>
+        <v>-0.422410180626741</v>
       </c>
       <c r="I13" s="3" t="s">
         <v>703</v>
@@ -52977,7 +52977,7 @@
       </c>
       <c r="D14" s="16" t="n">
         <f aca="false">C14/B14-1</f>
-        <v>-0.196445911051257</v>
+        <v>-0.196445911051256</v>
       </c>
       <c r="E14" s="22" t="n">
         <f aca="false">PL!F147</f>
@@ -52985,15 +52985,15 @@
       </c>
       <c r="F14" s="16" t="n">
         <f aca="false">E14/B14-1</f>
-        <v>-0.349690194293782</v>
+        <v>-0.349690194293781</v>
       </c>
       <c r="G14" s="22" t="n">
         <f aca="false">PL!F193</f>
-        <v>10.8614617105726</v>
+        <v>10.8614617105727</v>
       </c>
       <c r="H14" s="16" t="n">
         <f aca="false">G14/B14-1</f>
-        <v>-0.509197392201869</v>
+        <v>-0.509197392201868</v>
       </c>
       <c r="I14" s="3" t="s">
         <v>703</v>
@@ -53016,7 +53016,7 @@
       </c>
       <c r="D15" s="16" t="n">
         <f aca="false">C15/B15-1</f>
-        <v>-0.317626554549667</v>
+        <v>-0.317626554549666</v>
       </c>
       <c r="E15" s="22" t="n">
         <f aca="false">PL!F147</f>
@@ -53024,15 +53024,15 @@
       </c>
       <c r="F15" s="16" t="n">
         <f aca="false">E15/B15-1</f>
-        <v>-0.447760706052241</v>
+        <v>-0.44776070605224</v>
       </c>
       <c r="G15" s="22" t="n">
         <f aca="false">PL!F193</f>
-        <v>10.8614617105726</v>
+        <v>10.8614617105727</v>
       </c>
       <c r="H15" s="16" t="n">
         <f aca="false">G15/B15-1</f>
-        <v>-0.583213288159147</v>
+        <v>-0.583213288159146</v>
       </c>
       <c r="I15" s="3" t="s">
         <v>706</v>
@@ -53365,7 +53365,7 @@
       </c>
       <c r="C25" s="16" t="n">
         <f aca="false">PL!D73</f>
-        <v>0.247531793970354</v>
+        <v>0.247531793970355</v>
       </c>
       <c r="D25" s="16" t="n">
         <f aca="false">C25-B25</f>
@@ -53373,7 +53373,7 @@
       </c>
       <c r="E25" s="16" t="n">
         <f aca="false">PL!D119</f>
-        <v>0.247531793970354</v>
+        <v>0.247531793970355</v>
       </c>
       <c r="F25" s="16" t="n">
         <f aca="false">E25-B25</f>
@@ -53381,7 +53381,7 @@
       </c>
       <c r="G25" s="16" t="n">
         <f aca="false">PL!D165</f>
-        <v>0.247531793970354</v>
+        <v>0.247531793970355</v>
       </c>
       <c r="H25" s="16" t="n">
         <f aca="false">G25-B25</f>
@@ -53428,7 +53428,7 @@
       </c>
       <c r="C28" s="16" t="n">
         <f aca="false">PL!F86</f>
-        <v>0.986312346288996</v>
+        <v>0.986312346288997</v>
       </c>
       <c r="E28" s="16" t="n">
         <f aca="false">PL!F132</f>
@@ -53436,7 +53436,7 @@
       </c>
       <c r="G28" s="16" t="n">
         <f aca="false">PL!F178</f>
-        <v>0.656607401649751</v>
+        <v>0.656607401649752</v>
       </c>
       <c r="I28" s="7" t="s">
         <v>111</v>
@@ -53636,11 +53636,11 @@
       </c>
       <c r="H4" s="21" t="n">
         <f aca="false">PL!F83</f>
-        <v>64.5810970084141</v>
+        <v>64.5810970084142</v>
       </c>
       <c r="I4" s="21" t="n">
         <f aca="false">PL!F81</f>
-        <v>53.9704970084141</v>
+        <v>53.9704970084142</v>
       </c>
       <c r="J4" s="16" t="n">
         <f aca="false">PL!F92</f>
@@ -53680,7 +53680,7 @@
       </c>
       <c r="G5" s="16" t="n">
         <f aca="false">F5/F$4-1</f>
-        <v>-0.0596151386578203</v>
+        <v>-0.0596151386578189</v>
       </c>
       <c r="H5" s="21" t="n">
         <f aca="false">F68</f>
@@ -53700,7 +53700,7 @@
       </c>
       <c r="L5" s="16" t="n">
         <f aca="false">K5/K$4-1</f>
-        <v>-0.208897962755878</v>
+        <v>-0.208897962755877</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -53748,7 +53748,7 @@
       </c>
       <c r="L6" s="16" t="n">
         <f aca="false">K6/K$4-1</f>
-        <v>0.0158344400969188</v>
+        <v>0.0158344400969173</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -53780,11 +53780,11 @@
       </c>
       <c r="H7" s="21" t="n">
         <f aca="false">F160</f>
-        <v>60.4924229926252</v>
+        <v>60.4924229926253</v>
       </c>
       <c r="I7" s="21" t="n">
         <f aca="false">F158</f>
-        <v>49.8818229926252</v>
+        <v>49.8818229926253</v>
       </c>
       <c r="J7" s="16" t="n">
         <f aca="false">F169</f>
@@ -53796,7 +53796,7 @@
       </c>
       <c r="L7" s="16" t="n">
         <f aca="false">K7/K$4-1</f>
-        <v>-0.072237921235328</v>
+        <v>-0.0722379212353281</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -53844,7 +53844,7 @@
       </c>
       <c r="L8" s="16" t="n">
         <f aca="false">K8/K$4-1</f>
-        <v>0.0158344400969188</v>
+        <v>0.0158344400969173</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -53856,11 +53856,11 @@
       </c>
       <c r="C9" s="21" t="n">
         <f aca="false">E252</f>
-        <v>43.6828664338562</v>
+        <v>43.6828664338563</v>
       </c>
       <c r="D9" s="21" t="n">
         <f aca="false">E250</f>
-        <v>33.0722664338562</v>
+        <v>33.0722664338563</v>
       </c>
       <c r="E9" s="16" t="n">
         <f aca="false">E261</f>
@@ -53872,15 +53872,15 @@
       </c>
       <c r="G9" s="16" t="n">
         <f aca="false">F9/F$4-1</f>
-        <v>-0.102055550943475</v>
+        <v>-0.102055550943474</v>
       </c>
       <c r="H9" s="21" t="n">
         <f aca="false">F252</f>
-        <v>51.0884727563106</v>
+        <v>51.0884727563107</v>
       </c>
       <c r="I9" s="21" t="n">
         <f aca="false">F250</f>
-        <v>40.4778727563106</v>
+        <v>40.4778727563107</v>
       </c>
       <c r="J9" s="16" t="n">
         <f aca="false">F261</f>
@@ -53940,7 +53940,7 @@
       </c>
       <c r="L10" s="16" t="n">
         <f aca="false">K10/K$4-1</f>
-        <v>0.0158344400969188</v>
+        <v>0.0158344400969173</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -53972,11 +53972,11 @@
       </c>
       <c r="H11" s="21" t="n">
         <f aca="false">F344</f>
-        <v>60.6863188737863</v>
+        <v>60.6863188737864</v>
       </c>
       <c r="I11" s="21" t="n">
         <f aca="false">F342</f>
-        <v>50.0757188737863</v>
+        <v>50.0757188737864</v>
       </c>
       <c r="J11" s="16" t="n">
         <f aca="false">F353</f>
@@ -54084,7 +54084,7 @@
       </c>
       <c r="L13" s="16" t="n">
         <f aca="false">K13/K$4-1</f>
-        <v>-0.199806829655691</v>
+        <v>-0.199806829655692</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -54096,11 +54096,11 @@
       </c>
       <c r="C14" s="21" t="n">
         <f aca="false">E482</f>
-        <v>53.132085414958</v>
+        <v>53.1320854149581</v>
       </c>
       <c r="D14" s="21" t="n">
         <f aca="false">E480</f>
-        <v>42.521485414958</v>
+        <v>42.5214854149581</v>
       </c>
       <c r="E14" s="16" t="n">
         <f aca="false">E491</f>
@@ -54112,15 +54112,15 @@
       </c>
       <c r="G14" s="16" t="n">
         <f aca="false">F14/F$4-1</f>
-        <v>0.131366716627626</v>
+        <v>0.131366716627627</v>
       </c>
       <c r="H14" s="21" t="n">
         <f aca="false">F482</f>
-        <v>64.5810970084141</v>
+        <v>64.5810970084142</v>
       </c>
       <c r="I14" s="21" t="n">
         <f aca="false">F480</f>
-        <v>53.9704970084141</v>
+        <v>53.9704970084142</v>
       </c>
       <c r="J14" s="16" t="n">
         <f aca="false">F491</f>
@@ -54164,11 +54164,11 @@
       </c>
       <c r="H15" s="21" t="n">
         <f aca="false">F528</f>
-        <v>64.5810970084141</v>
+        <v>64.5810970084142</v>
       </c>
       <c r="I15" s="21" t="n">
         <f aca="false">F526</f>
-        <v>53.9704970084141</v>
+        <v>53.9704970084142</v>
       </c>
       <c r="J15" s="16" t="n">
         <f aca="false">F537</f>
@@ -54180,7 +54180,7 @@
       </c>
       <c r="L15" s="16" t="n">
         <f aca="false">K15/K$4-1</f>
-        <v>-0.0803597194462411</v>
+        <v>-0.0803597194462412</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -54212,11 +54212,11 @@
       </c>
       <c r="H16" s="21" t="n">
         <f aca="false">F574</f>
-        <v>64.5810970084141</v>
+        <v>64.5810970084142</v>
       </c>
       <c r="I16" s="21" t="n">
         <f aca="false">F572</f>
-        <v>53.9704970084141</v>
+        <v>53.9704970084142</v>
       </c>
       <c r="J16" s="16" t="n">
         <f aca="false">F583</f>
@@ -54240,11 +54240,11 @@
       </c>
       <c r="C17" s="21" t="n">
         <f aca="false">E620</f>
-        <v>44.6277883319664</v>
+        <v>44.6277883319665</v>
       </c>
       <c r="D17" s="21" t="n">
         <f aca="false">E618</f>
-        <v>34.0171883319664</v>
+        <v>34.0171883319665</v>
       </c>
       <c r="E17" s="16" t="n">
         <f aca="false">E629</f>
@@ -54256,15 +54256,15 @@
       </c>
       <c r="G17" s="16" t="n">
         <f aca="false">F17/F$4-1</f>
-        <v>-0.0787133241863648</v>
+        <v>-0.0787133241863633</v>
       </c>
       <c r="H17" s="21" t="n">
         <f aca="false">F620</f>
-        <v>53.7869976067313</v>
+        <v>53.7869976067314</v>
       </c>
       <c r="I17" s="21" t="n">
         <f aca="false">F618</f>
-        <v>43.1763976067313</v>
+        <v>43.1763976067314</v>
       </c>
       <c r="J17" s="16" t="n">
         <f aca="false">F629</f>
@@ -54324,7 +54324,7 @@
       </c>
       <c r="L18" s="16" t="n">
         <f aca="false">K18/K$4-1</f>
-        <v>0.0158344400969188</v>
+        <v>0.0158344400969173</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -54356,11 +54356,11 @@
       </c>
       <c r="H19" s="21" t="n">
         <f aca="false">F712</f>
-        <v>64.5810970084141</v>
+        <v>64.5810970084142</v>
       </c>
       <c r="I19" s="21" t="n">
         <f aca="false">F710</f>
-        <v>53.9704970084141</v>
+        <v>53.9704970084142</v>
       </c>
       <c r="J19" s="16" t="n">
         <f aca="false">F721</f>
@@ -54372,7 +54372,7 @@
       </c>
       <c r="L19" s="16" t="n">
         <f aca="false">K19/K$4-1</f>
-        <v>-0.0356914713601556</v>
+        <v>-0.0356914713601557</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -54404,11 +54404,11 @@
       </c>
       <c r="H20" s="21" t="n">
         <f aca="false">F758</f>
-        <v>64.5810970084141</v>
+        <v>64.5810970084142</v>
       </c>
       <c r="I20" s="21" t="n">
         <f aca="false">F756</f>
-        <v>53.9704970084141</v>
+        <v>53.9704970084142</v>
       </c>
       <c r="J20" s="16" t="n">
         <f aca="false">F767</f>
@@ -54452,11 +54452,11 @@
       </c>
       <c r="H21" s="21" t="n">
         <f aca="false">F804</f>
-        <v>63.5465635084141</v>
+        <v>63.5465635084142</v>
       </c>
       <c r="I21" s="21" t="n">
         <f aca="false">F802</f>
-        <v>53.9704970084141</v>
+        <v>53.9704970084142</v>
       </c>
       <c r="J21" s="16" t="n">
         <f aca="false">F813</f>
@@ -54464,11 +54464,11 @@
       </c>
       <c r="K21" s="17" t="n">
         <f aca="false">F822</f>
-        <v>17.5955460965734</v>
+        <v>17.5955460965735</v>
       </c>
       <c r="L21" s="16" t="n">
         <f aca="false">K21/K$4-1</f>
-        <v>-0.0105218216036574</v>
+        <v>-0.0105218216036572</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -54516,7 +54516,7 @@
       </c>
       <c r="L22" s="16" t="n">
         <f aca="false">K22/K$4-1</f>
-        <v>0.00768056917280457</v>
+        <v>0.00768056917280324</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -54548,11 +54548,11 @@
       </c>
       <c r="H23" s="21" t="n">
         <f aca="false">F896</f>
-        <v>64.5810970084141</v>
+        <v>64.5810970084142</v>
       </c>
       <c r="I23" s="21" t="n">
         <f aca="false">F894</f>
-        <v>53.9704970084141</v>
+        <v>53.9704970084142</v>
       </c>
       <c r="J23" s="16" t="n">
         <f aca="false">F905</f>
@@ -54560,11 +54560,11 @@
       </c>
       <c r="K23" s="17" t="n">
         <f aca="false">F914</f>
-        <v>16.8511961429311</v>
+        <v>16.8511961429312</v>
       </c>
       <c r="L23" s="16" t="n">
         <f aca="false">K23/K$4-1</f>
-        <v>-0.0523800300489652</v>
+        <v>-0.0523800300489651</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -54596,11 +54596,11 @@
       </c>
       <c r="H24" s="21" t="n">
         <f aca="false">PL!F129</f>
-        <v>53.7869976067313</v>
+        <v>53.7869976067314</v>
       </c>
       <c r="I24" s="21" t="n">
         <f aca="false">PL!F127</f>
-        <v>43.1763976067313</v>
+        <v>43.1763976067314</v>
       </c>
       <c r="J24" s="16" t="n">
         <f aca="false">PL!F138</f>
@@ -54612,7 +54612,7 @@
       </c>
       <c r="L24" s="16" t="n">
         <f aca="false">K24/K$4-1</f>
-        <v>-0.190708112061265</v>
+        <v>-0.190708112061266</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -54656,7 +54656,7 @@
       </c>
       <c r="K25" s="17" t="n">
         <f aca="false">PL!F193</f>
-        <v>10.8614617105726</v>
+        <v>10.8614617105727</v>
       </c>
       <c r="L25" s="16" t="n">
         <f aca="false">K25/K$4-1</f>
@@ -54706,11 +54706,11 @@
       </c>
       <c r="D31" s="17" t="n">
         <f aca="false">Val!B35</f>
-        <v>442.977340230993</v>
+        <v>442.977340230994</v>
       </c>
       <c r="E31" s="17" t="n">
         <f aca="false">tp_w_dcf*C31+(1-tp_w_dcf)*D31</f>
-        <v>322.84375955125</v>
+        <v>322.843759551251</v>
       </c>
       <c r="F31" s="16" t="n">
         <f aca="false">E31/E$31-1</f>
@@ -54730,11 +54730,11 @@
       </c>
       <c r="D32" s="17" t="n">
         <f aca="false">Val!B35</f>
-        <v>442.977340230993</v>
+        <v>442.977340230994</v>
       </c>
       <c r="E32" s="17" t="n">
         <f aca="false">tp_w_dcf*C32+(1-tp_w_dcf)*D32</f>
-        <v>309.299465836654</v>
+        <v>309.299465836655</v>
       </c>
       <c r="F32" s="16" t="n">
         <f aca="false">E32/E$31-1</f>
@@ -54754,11 +54754,11 @@
       </c>
       <c r="D33" s="17" t="n">
         <f aca="false">Val!B35</f>
-        <v>442.977340230993</v>
+        <v>442.977340230994</v>
       </c>
       <c r="E33" s="17" t="n">
         <f aca="false">tp_w_dcf*C33+(1-tp_w_dcf)*D33</f>
-        <v>341.790908307035</v>
+        <v>341.790908307036</v>
       </c>
       <c r="F33" s="16" t="n">
         <f aca="false">E33/E$31-1</f>
@@ -54778,7 +54778,7 @@
       </c>
       <c r="D34" s="17" t="n">
         <f aca="false">Val!B35</f>
-        <v>442.977340230993</v>
+        <v>442.977340230994</v>
       </c>
       <c r="E34" s="17" t="n">
         <f aca="false">tp_w_dcf*C34+(1-tp_w_dcf)*D34</f>
@@ -54786,7 +54786,7 @@
       </c>
       <c r="F34" s="16" t="n">
         <f aca="false">E34/E$31-1</f>
-        <v>0.0236943944072308</v>
+        <v>0.023694394407231</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -54802,7 +54802,7 @@
       </c>
       <c r="D35" s="17" t="n">
         <f aca="false">Val!B35</f>
-        <v>442.977340230993</v>
+        <v>442.977340230994</v>
       </c>
       <c r="E35" s="17" t="n">
         <f aca="false">tp_w_dcf*C35+(1-tp_w_dcf)*D35</f>
@@ -54810,7 +54810,7 @@
       </c>
       <c r="F35" s="16" t="n">
         <f aca="false">E35/E$31-1</f>
-        <v>-0.0154612221634481</v>
+        <v>-0.015461222163448</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -54823,7 +54823,7 @@
       </c>
       <c r="D36" s="17" t="n">
         <f aca="false">Val!B35</f>
-        <v>442.977340230993</v>
+        <v>442.977340230994</v>
       </c>
       <c r="E36" s="17" t="n">
         <f aca="false">0.4*C36+(1-0.4)*D36</f>
@@ -54831,7 +54831,7 @@
       </c>
       <c r="F36" s="16" t="n">
         <f aca="false">E36/E$31-1</f>
-        <v>0.07442211727848</v>
+        <v>0.0744221172784803</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -54844,11 +54844,11 @@
       </c>
       <c r="D37" s="17" t="n">
         <f aca="false">Val!B35</f>
-        <v>442.977340230993</v>
+        <v>442.977340230994</v>
       </c>
       <c r="E37" s="17" t="n">
         <f aca="false">0.8*C37+(1-0.8)*D37</f>
-        <v>250.763611143404</v>
+        <v>250.763611143405</v>
       </c>
       <c r="F37" s="16" t="n">
         <f aca="false">E37/E$31-1</f>
@@ -54909,7 +54909,7 @@
       </c>
       <c r="D48" s="22" t="n">
         <f aca="false">itc_26*1</f>
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="E48" s="22" t="n">
         <f aca="false">itc_27*1*1</f>
@@ -55077,7 +55077,7 @@
       </c>
       <c r="D55" s="22" t="n">
         <f aca="false">D50*D54/1000</f>
-        <v>10.5297921189288</v>
+        <v>10.5297921189287</v>
       </c>
       <c r="E55" s="22" t="n">
         <f aca="false">E50*E54/1000</f>
@@ -55101,7 +55101,7 @@
       </c>
       <c r="D56" s="21" t="n">
         <f aca="false">D55*fx</f>
-        <v>70.7602030392013</v>
+        <v>70.7602030392012</v>
       </c>
       <c r="E56" s="21" t="n">
         <f aca="false">E55*fx</f>
@@ -55149,7 +55149,7 @@
       </c>
       <c r="D58" s="16" t="n">
         <f aca="false">a26_ai/D56</f>
-        <v>0.247531793970354</v>
+        <v>0.247531793970355</v>
       </c>
       <c r="K58" s="7" t="s">
         <v>510</v>
@@ -55188,7 +55188,7 @@
       </c>
       <c r="D60" s="16" t="n">
         <f aca="false">$D$58*D59</f>
-        <v>0.247531793970354</v>
+        <v>0.247531793970355</v>
       </c>
       <c r="E60" s="16" t="n">
         <f aca="false">$D$58*E59</f>
@@ -55196,7 +55196,7 @@
       </c>
       <c r="F60" s="16" t="n">
         <f aca="false">$D$58*F59</f>
-        <v>0.198025435176283</v>
+        <v>0.198025435176284</v>
       </c>
       <c r="G60" s="16" t="n">
         <f aca="false">$D$58*G59</f>
@@ -55388,7 +55388,7 @@
       </c>
       <c r="H68" s="23" t="n">
         <f aca="false">G68*(1+H69)</f>
-        <v>59.9908462497548</v>
+        <v>59.9908462497549</v>
       </c>
       <c r="I68" s="23" t="n">
         <f aca="false">H68*(1+I69)</f>
@@ -55396,7 +55396,7 @@
       </c>
       <c r="J68" s="23" t="n">
         <f aca="false">I68*(1+J69)</f>
-        <v>67.5759245877639</v>
+        <v>67.575924587764</v>
       </c>
       <c r="K68" s="7" t="s">
         <v>521</v>
@@ -55415,7 +55415,7 @@
       </c>
       <c r="E69" s="16" t="n">
         <f aca="false">E68/D68-1</f>
-        <v>0.614197050721823</v>
+        <v>0.614197050721825</v>
       </c>
       <c r="F69" s="16" t="n">
         <f aca="false">F68/E68-1</f>
@@ -55455,11 +55455,11 @@
       </c>
       <c r="E70" s="16" t="n">
         <f aca="false">E66/E68</f>
-        <v>0.766291008776356</v>
+        <v>0.766291008776357</v>
       </c>
       <c r="F70" s="16" t="n">
         <f aca="false">F66/F68</f>
-        <v>0.798751771500277</v>
+        <v>0.798751771500278</v>
       </c>
       <c r="G70" s="16" t="n">
         <f aca="false">G66/G68</f>
@@ -55479,15 +55479,15 @@
       </c>
       <c r="E71" s="16" t="n">
         <f aca="false">(E61+E65)/E64</f>
-        <v>0.94952767689519</v>
+        <v>0.949527676895191</v>
       </c>
       <c r="F71" s="16" t="n">
         <f aca="false">(F61+F65)/F64</f>
-        <v>0.805224403210623</v>
+        <v>0.805224403210624</v>
       </c>
       <c r="G71" s="16" t="n">
         <f aca="false">(G61+G65)/G64</f>
-        <v>0.709960590817844</v>
+        <v>0.709960590817845</v>
       </c>
       <c r="K71" s="3" t="s">
         <v>525</v>
@@ -55502,7 +55502,7 @@
       </c>
       <c r="D72" s="20" t="n">
         <f aca="false">D66/fx/D50*1000</f>
-        <v>111.389307286659</v>
+        <v>111.38930728666</v>
       </c>
       <c r="E72" s="20" t="n">
         <f aca="false">E66/fx/E50*1000</f>
@@ -55637,11 +55637,11 @@
       </c>
       <c r="E78" s="21" t="n">
         <f aca="false">D78*(1+MAX(0,phi*E69))</f>
-        <v>2.5015213159998</v>
+        <v>2.50152131599981</v>
       </c>
       <c r="F78" s="21" t="n">
         <f aca="false">E78*(1+MAX(0,phi*F69))</f>
-        <v>2.74361424916849</v>
+        <v>2.7436142491685</v>
       </c>
       <c r="G78" s="21" t="n">
         <f aca="false">F78*(1+MAX(0,phi*G69))</f>
@@ -55668,11 +55668,11 @@
       </c>
       <c r="E79" s="21" t="n">
         <f aca="false">E78+0*E68</f>
-        <v>2.5015213159998</v>
+        <v>2.50152131599981</v>
       </c>
       <c r="F79" s="21" t="n">
         <f aca="false">F78+0*F68</f>
-        <v>2.74361424916849</v>
+        <v>2.7436142491685</v>
       </c>
       <c r="G79" s="21" t="n">
         <f aca="false">G78+0*G68</f>
@@ -55779,7 +55779,7 @@
       </c>
       <c r="F83" s="21" t="n">
         <f aca="false">(F80+F82)*nir_f</f>
-        <v>13.8194532391262</v>
+        <v>13.8194532391263</v>
       </c>
       <c r="G83" s="21" t="n">
         <f aca="false">(G80+G82)*nir_f</f>
@@ -55922,15 +55922,15 @@
       </c>
       <c r="E87" s="16" t="n">
         <f aca="false">E86/D86-1</f>
-        <v>0.741296051904864</v>
+        <v>0.741296051904867</v>
       </c>
       <c r="F87" s="16" t="n">
         <f aca="false">F86/E86-1</f>
-        <v>0.167953816117978</v>
+        <v>0.167953816117979</v>
       </c>
       <c r="G87" s="16" t="n">
         <f aca="false">G86/F86-1</f>
-        <v>0.051299318261169</v>
+        <v>0.0512993182611685</v>
       </c>
       <c r="H87" s="24" t="n">
         <f aca="false">H86/G86-1</f>
@@ -55938,11 +55938,11 @@
       </c>
       <c r="I87" s="24" t="n">
         <f aca="false">I86/H86-1</f>
-        <v>0.0754818599598475</v>
+        <v>0.0754818599598472</v>
       </c>
       <c r="J87" s="24" t="n">
         <f aca="false">J86/I86-1</f>
-        <v>0.0726208634262882</v>
+        <v>0.0726208634262879</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -55962,7 +55962,7 @@
       </c>
       <c r="E88" s="16" t="n">
         <f aca="false">E83/E68</f>
-        <v>0.260615756334691</v>
+        <v>0.260615756334692</v>
       </c>
       <c r="F88" s="16" t="n">
         <f aca="false">F83/F68</f>
@@ -56039,7 +56039,7 @@
       </c>
       <c r="D94" s="22" t="n">
         <f aca="false">itc_26*1</f>
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="E94" s="22" t="n">
         <f aca="false">itc_27*1*1</f>
@@ -56207,7 +56207,7 @@
       </c>
       <c r="D101" s="22" t="n">
         <f aca="false">D96*D100/1000</f>
-        <v>10.5297921189288</v>
+        <v>10.5297921189287</v>
       </c>
       <c r="E101" s="22" t="n">
         <f aca="false">E96*E100/1000</f>
@@ -56231,7 +56231,7 @@
       </c>
       <c r="D102" s="21" t="n">
         <f aca="false">D101*fx</f>
-        <v>70.7602030392013</v>
+        <v>70.7602030392012</v>
       </c>
       <c r="E102" s="21" t="n">
         <f aca="false">E101*fx</f>
@@ -56279,7 +56279,7 @@
       </c>
       <c r="D104" s="16" t="n">
         <f aca="false">a26_ai/D102</f>
-        <v>0.247531793970354</v>
+        <v>0.247531793970355</v>
       </c>
       <c r="K104" s="7" t="s">
         <v>510</v>
@@ -56318,7 +56318,7 @@
       </c>
       <c r="D106" s="16" t="n">
         <f aca="false">$D$104*D105</f>
-        <v>0.247531793970354</v>
+        <v>0.247531793970355</v>
       </c>
       <c r="E106" s="16" t="n">
         <f aca="false">$D$104*E105</f>
@@ -56326,7 +56326,7 @@
       </c>
       <c r="F106" s="16" t="n">
         <f aca="false">$D$104*F105</f>
-        <v>0.198025435176283</v>
+        <v>0.198025435176284</v>
       </c>
       <c r="G106" s="16" t="n">
         <f aca="false">$D$104*G105</f>
@@ -56346,15 +56346,15 @@
       </c>
       <c r="E107" s="21" t="n">
         <f aca="false">E102*E106*E103</f>
-        <v>50.6267538958151</v>
+        <v>50.6267538958152</v>
       </c>
       <c r="F107" s="21" t="n">
         <f aca="false">F102*F106*F103</f>
-        <v>66.9179647250791</v>
+        <v>66.9179647250792</v>
       </c>
       <c r="G107" s="21" t="n">
         <f aca="false">G102*G106*G103</f>
-        <v>78.8468662329983</v>
+        <v>78.8468662329985</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -56632,7 +56632,7 @@
       </c>
       <c r="D118" s="20" t="n">
         <f aca="false">D112/fx/D96*1000</f>
-        <v>111.389307286659</v>
+        <v>111.38930728666</v>
       </c>
       <c r="E118" s="20" t="n">
         <f aca="false">E112/fx/E96*1000</f>
@@ -57169,7 +57169,7 @@
       </c>
       <c r="D140" s="22" t="n">
         <f aca="false">itc_26*1</f>
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="E140" s="22" t="n">
         <f aca="false">itc_27*1*1</f>
@@ -57337,7 +57337,7 @@
       </c>
       <c r="D147" s="22" t="n">
         <f aca="false">D142*D146/1000</f>
-        <v>10.5297921189288</v>
+        <v>10.5297921189287</v>
       </c>
       <c r="E147" s="22" t="n">
         <f aca="false">E142*E146/1000</f>
@@ -57361,7 +57361,7 @@
       </c>
       <c r="D148" s="21" t="n">
         <f aca="false">D147*fx</f>
-        <v>70.7602030392013</v>
+        <v>70.7602030392012</v>
       </c>
       <c r="E148" s="21" t="n">
         <f aca="false">E147*fx</f>
@@ -57409,7 +57409,7 @@
       </c>
       <c r="D150" s="16" t="n">
         <f aca="false">a26_ai/D148</f>
-        <v>0.247531793970354</v>
+        <v>0.247531793970355</v>
       </c>
       <c r="K150" s="7" t="s">
         <v>510</v>
@@ -57448,7 +57448,7 @@
       </c>
       <c r="D152" s="16" t="n">
         <f aca="false">$D$150*D151</f>
-        <v>0.247531793970354</v>
+        <v>0.247531793970355</v>
       </c>
       <c r="E152" s="16" t="n">
         <f aca="false">$D$150*E151</f>
@@ -57456,7 +57456,7 @@
       </c>
       <c r="F152" s="16" t="n">
         <f aca="false">$D$150*F151</f>
-        <v>0.198025435176283</v>
+        <v>0.198025435176284</v>
       </c>
       <c r="G152" s="16" t="n">
         <f aca="false">$D$150*G151</f>
@@ -57476,11 +57476,11 @@
       </c>
       <c r="E153" s="21" t="n">
         <f aca="false">E148*E152*E149</f>
-        <v>40.6510388424525</v>
+        <v>40.6510388424526</v>
       </c>
       <c r="F153" s="21" t="n">
         <f aca="false">F148*F152*F149</f>
-        <v>49.8818229926252</v>
+        <v>49.8818229926253</v>
       </c>
       <c r="G153" s="21" t="n">
         <f aca="false">G148*G152*G149</f>
@@ -57592,7 +57592,7 @@
       </c>
       <c r="F158" s="21" t="n">
         <f aca="false">MIN(F153,F156-F157)</f>
-        <v>49.8818229926252</v>
+        <v>49.8818229926253</v>
       </c>
       <c r="G158" s="21" t="n">
         <f aca="false">MIN(G153,G156-G157)</f>
@@ -57640,7 +57640,7 @@
       </c>
       <c r="F160" s="21" t="n">
         <f aca="false">F158+F157</f>
-        <v>60.4924229926252</v>
+        <v>60.4924229926253</v>
       </c>
       <c r="G160" s="21" t="n">
         <f aca="false">G158+G157</f>
@@ -57648,15 +57648,15 @@
       </c>
       <c r="H160" s="23" t="n">
         <f aca="false">G160*(1+H161)</f>
-        <v>73.4594454761412</v>
+        <v>73.4594454761413</v>
       </c>
       <c r="I160" s="23" t="n">
         <f aca="false">H160*(1+I161)</f>
-        <v>79.1014561012266</v>
+        <v>79.1014561012267</v>
       </c>
       <c r="J160" s="23" t="n">
         <f aca="false">I160*(1+J161)</f>
-        <v>83.8475434673002</v>
+        <v>83.8475434673003</v>
       </c>
       <c r="K160" s="7" t="s">
         <v>521</v>
@@ -57679,7 +57679,7 @@
       </c>
       <c r="F161" s="16" t="n">
         <f aca="false">F160/E160-1</f>
-        <v>0.265156020442153</v>
+        <v>0.265156020442154</v>
       </c>
       <c r="G161" s="16" t="n">
         <f aca="false">G160/F160-1</f>
@@ -57687,11 +57687,11 @@
       </c>
       <c r="H161" s="24" t="n">
         <f aca="false">$G161+(fade_gA-$G161)*1/3</f>
-        <v>0.0936088542056267</v>
+        <v>0.0936088542056268</v>
       </c>
       <c r="I161" s="24" t="n">
         <f aca="false">$G161+(fade_gA-$G161)*2/3</f>
-        <v>0.0768044271028133</v>
+        <v>0.0768044271028134</v>
       </c>
       <c r="J161" s="24" t="n">
         <f aca="false">$G161+(fade_gA-$G161)*3/3</f>
@@ -57719,7 +57719,7 @@
       </c>
       <c r="F162" s="16" t="n">
         <f aca="false">F158/F160</f>
-        <v>0.824596214284662</v>
+        <v>0.824596214284663</v>
       </c>
       <c r="G162" s="16" t="n">
         <f aca="false">G158/G160</f>
@@ -57743,11 +57743,11 @@
       </c>
       <c r="F163" s="16" t="n">
         <f aca="false">(F153+F157)/F156</f>
-        <v>0.923868227986108</v>
+        <v>0.923868227986109</v>
       </c>
       <c r="G163" s="16" t="n">
         <f aca="false">(G153+G157)/G156</f>
-        <v>0.846893007675428</v>
+        <v>0.84689300767543</v>
       </c>
       <c r="K163" s="3" t="s">
         <v>525</v>
@@ -57762,7 +57762,7 @@
       </c>
       <c r="D164" s="20" t="n">
         <f aca="false">D158/fx/D142*1000</f>
-        <v>111.389307286659</v>
+        <v>111.38930728666</v>
       </c>
       <c r="E164" s="20" t="n">
         <f aca="false">E158/fx/E142*1000</f>
@@ -57849,7 +57849,7 @@
       </c>
       <c r="G168" s="21" t="n">
         <f aca="false">G158*G167+G157*$D$166</f>
-        <v>23.9223705320389</v>
+        <v>23.922370532039</v>
       </c>
     </row>
     <row r="169" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -58162,7 +58162,7 @@
       </c>
       <c r="I178" s="28" t="n">
         <f aca="false">I175/I177</f>
-        <v>21.4641816487849</v>
+        <v>21.464181648785</v>
       </c>
       <c r="J178" s="28" t="n">
         <f aca="false">J175/J177</f>
@@ -58186,11 +58186,11 @@
       </c>
       <c r="F179" s="16" t="n">
         <f aca="false">F178/E178-1</f>
-        <v>0.288057982482072</v>
+        <v>0.288057982482074</v>
       </c>
       <c r="G179" s="16" t="n">
         <f aca="false">G178/F178-1</f>
-        <v>0.0974500625336581</v>
+        <v>0.0974500625336583</v>
       </c>
       <c r="H179" s="24" t="n">
         <f aca="false">H178/G178-1</f>
@@ -58202,7 +58202,7 @@
       </c>
       <c r="J179" s="24" t="n">
         <f aca="false">J178/I178-1</f>
-        <v>0.0635243386128743</v>
+        <v>0.0635243386128741</v>
       </c>
     </row>
     <row r="180" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -58299,7 +58299,7 @@
       </c>
       <c r="D186" s="22" t="n">
         <f aca="false">itc_26*1</f>
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="E186" s="22" t="n">
         <f aca="false">itc_27*1*1</f>
@@ -58467,7 +58467,7 @@
       </c>
       <c r="D193" s="22" t="n">
         <f aca="false">D188*D192/1000</f>
-        <v>10.5297921189288</v>
+        <v>10.5297921189287</v>
       </c>
       <c r="E193" s="22" t="n">
         <f aca="false">E188*E192/1000</f>
@@ -58491,7 +58491,7 @@
       </c>
       <c r="D194" s="21" t="n">
         <f aca="false">D193*fx</f>
-        <v>70.7602030392013</v>
+        <v>70.7602030392012</v>
       </c>
       <c r="E194" s="21" t="n">
         <f aca="false">E193*fx</f>
@@ -58539,7 +58539,7 @@
       </c>
       <c r="D196" s="16" t="n">
         <f aca="false">a26_ai/D194</f>
-        <v>0.247531793970354</v>
+        <v>0.247531793970355</v>
       </c>
       <c r="K196" s="7" t="s">
         <v>510</v>
@@ -58578,7 +58578,7 @@
       </c>
       <c r="D198" s="16" t="n">
         <f aca="false">$D$196*D197</f>
-        <v>0.247531793970354</v>
+        <v>0.247531793970355</v>
       </c>
       <c r="E198" s="16" t="n">
         <f aca="false">$D$196*E197</f>
@@ -58586,7 +58586,7 @@
       </c>
       <c r="F198" s="16" t="n">
         <f aca="false">$D$196*F197</f>
-        <v>0.198025435176283</v>
+        <v>0.198025435176284</v>
       </c>
       <c r="G198" s="16" t="n">
         <f aca="false">$D$196*G197</f>
@@ -58606,15 +58606,15 @@
       </c>
       <c r="E199" s="21" t="n">
         <f aca="false">E194*E198*E195</f>
-        <v>44.3919319874635</v>
+        <v>44.3919319874636</v>
       </c>
       <c r="F199" s="21" t="n">
         <f aca="false">F194*F198*F195</f>
-        <v>57.3777253549049</v>
+        <v>57.377725354905</v>
       </c>
       <c r="G199" s="21" t="n">
         <f aca="false">G194*G198*G195</f>
-        <v>67.1397286706748</v>
+        <v>67.1397286706749</v>
       </c>
     </row>
     <row r="200" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -58726,7 +58726,7 @@
       </c>
       <c r="G204" s="21" t="n">
         <f aca="false">MIN(G199,G202-G203)</f>
-        <v>67.1397286706748</v>
+        <v>67.1397286706749</v>
       </c>
       <c r="K204" s="3" t="s">
         <v>519</v>
@@ -58774,19 +58774,19 @@
       </c>
       <c r="G206" s="21" t="n">
         <f aca="false">G204+G203</f>
-        <v>77.7503286706748</v>
+        <v>77.7503286706749</v>
       </c>
       <c r="H206" s="23" t="n">
         <f aca="false">G206*(1+H207)</f>
-        <v>89.0209611466437</v>
+        <v>89.0209611466439</v>
       </c>
       <c r="I206" s="23" t="n">
         <f aca="false">H206*(1+I207)</f>
-        <v>98.1437976623191</v>
+        <v>98.1437976623194</v>
       </c>
       <c r="J206" s="23" t="n">
         <f aca="false">I206*(1+J207)</f>
-        <v>104.032425522058</v>
+        <v>104.032425522059</v>
       </c>
       <c r="K206" s="7" t="s">
         <v>521</v>
@@ -58813,15 +58813,15 @@
       </c>
       <c r="G207" s="16" t="n">
         <f aca="false">G206/F206-1</f>
-        <v>0.187438935667546</v>
+        <v>0.187438935667547</v>
       </c>
       <c r="H207" s="24" t="n">
         <f aca="false">$G207+(fade_gA-$G207)*1/3</f>
-        <v>0.144959290445031</v>
+        <v>0.144959290445032</v>
       </c>
       <c r="I207" s="24" t="n">
         <f aca="false">$G207+(fade_gA-$G207)*2/3</f>
-        <v>0.102479645222515</v>
+        <v>0.102479645222516</v>
       </c>
       <c r="J207" s="24" t="n">
         <f aca="false">$G207+(fade_gA-$G207)*3/3</f>
@@ -58877,7 +58877,7 @@
       </c>
       <c r="G209" s="16" t="n">
         <f aca="false">(G199+G203)/G202</f>
-        <v>0.980268738380868</v>
+        <v>0.980268738380869</v>
       </c>
       <c r="K209" s="3" t="s">
         <v>525</v>
@@ -58892,7 +58892,7 @@
       </c>
       <c r="D210" s="20" t="n">
         <f aca="false">D204/fx/D188*1000</f>
-        <v>111.389307286659</v>
+        <v>111.38930728666</v>
       </c>
       <c r="E210" s="20" t="n">
         <f aca="false">E204/fx/E188*1000</f>
@@ -59173,7 +59173,7 @@
       </c>
       <c r="G221" s="21" t="n">
         <f aca="false">(G218+G220)*nir_f</f>
-        <v>20.9794650094605</v>
+        <v>20.9794650094606</v>
       </c>
       <c r="H221" s="23" t="n">
         <f aca="false">H206*H226</f>
@@ -59181,7 +59181,7 @@
       </c>
       <c r="I221" s="23" t="n">
         <f aca="false">I206*I226</f>
-        <v>26.326082217586</v>
+        <v>26.3260822175861</v>
       </c>
       <c r="J221" s="23" t="n">
         <f aca="false">J206*J226</f>
@@ -59288,15 +59288,15 @@
       </c>
       <c r="H224" s="28" t="n">
         <f aca="false">H221/H223</f>
-        <v>24.3803605969258</v>
+        <v>24.3803605969259</v>
       </c>
       <c r="I224" s="28" t="n">
         <f aca="false">I221/I223</f>
-        <v>26.7993588956838</v>
+        <v>26.7993588956839</v>
       </c>
       <c r="J224" s="28" t="n">
         <f aca="false">J221/J223</f>
-        <v>28.3230584794762</v>
+        <v>28.3230584794763</v>
       </c>
     </row>
     <row r="225" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -59320,11 +59320,11 @@
       </c>
       <c r="G225" s="16" t="n">
         <f aca="false">G224/F224-1</f>
-        <v>0.182260333575398</v>
+        <v>0.182260333575399</v>
       </c>
       <c r="H225" s="24" t="n">
         <f aca="false">H224/G224-1</f>
-        <v>0.141583134650197</v>
+        <v>0.141583134650198</v>
       </c>
       <c r="I225" s="24" t="n">
         <f aca="false">I224/H224-1</f>
@@ -59332,7 +59332,7 @@
       </c>
       <c r="J225" s="24" t="n">
         <f aca="false">J224/I224-1</f>
-        <v>0.0568558221755739</v>
+        <v>0.0568558221755742</v>
       </c>
     </row>
     <row r="226" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -59429,7 +59429,7 @@
       </c>
       <c r="D232" s="22" t="n">
         <f aca="false">itc_26*1</f>
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="E232" s="22" t="n">
         <f aca="false">itc_27*1*1</f>
@@ -59597,7 +59597,7 @@
       </c>
       <c r="D239" s="22" t="n">
         <f aca="false">D234*D238/1000</f>
-        <v>10.5297921189288</v>
+        <v>10.5297921189287</v>
       </c>
       <c r="E239" s="22" t="n">
         <f aca="false">E234*E238/1000</f>
@@ -59621,7 +59621,7 @@
       </c>
       <c r="D240" s="21" t="n">
         <f aca="false">D239*fx</f>
-        <v>70.7602030392013</v>
+        <v>70.7602030392012</v>
       </c>
       <c r="E240" s="21" t="n">
         <f aca="false">E239*fx</f>
@@ -59669,7 +59669,7 @@
       </c>
       <c r="D242" s="16" t="n">
         <f aca="false">a26_ai/D240</f>
-        <v>0.247531793970354</v>
+        <v>0.247531793970355</v>
       </c>
       <c r="K242" s="7" t="s">
         <v>510</v>
@@ -59708,7 +59708,7 @@
       </c>
       <c r="D244" s="16" t="n">
         <f aca="false">$D$242*D243</f>
-        <v>0.247531793970354</v>
+        <v>0.247531793970355</v>
       </c>
       <c r="E244" s="16" t="n">
         <f aca="false">$D$242*E243</f>
@@ -59716,7 +59716,7 @@
       </c>
       <c r="F244" s="16" t="n">
         <f aca="false">$D$242*F243</f>
-        <v>0.148519076382212</v>
+        <v>0.148519076382213</v>
       </c>
       <c r="G244" s="16" t="n">
         <f aca="false">$D$242*G243</f>
@@ -59736,15 +59736,15 @@
       </c>
       <c r="E245" s="21" t="n">
         <f aca="false">E240*E244*E241</f>
-        <v>33.0722664338562</v>
+        <v>33.0722664338563</v>
       </c>
       <c r="F245" s="21" t="n">
         <f aca="false">F240*F244*F241</f>
-        <v>40.4778727563106</v>
+        <v>40.4778727563107</v>
       </c>
       <c r="G245" s="21" t="n">
         <f aca="false">G240*G244*G241</f>
-        <v>45.3569301460784</v>
+        <v>45.3569301460785</v>
       </c>
     </row>
     <row r="246" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -59848,15 +59848,15 @@
       </c>
       <c r="E250" s="21" t="n">
         <f aca="false">MIN(E245,E248-E249)</f>
-        <v>33.0722664338562</v>
+        <v>33.0722664338563</v>
       </c>
       <c r="F250" s="21" t="n">
         <f aca="false">MIN(F245,F248-F249)</f>
-        <v>40.4778727563106</v>
+        <v>40.4778727563107</v>
       </c>
       <c r="G250" s="21" t="n">
         <f aca="false">MIN(G245,G248-G249)</f>
-        <v>45.3569301460784</v>
+        <v>45.3569301460785</v>
       </c>
       <c r="K250" s="3" t="s">
         <v>519</v>
@@ -59896,27 +59896,27 @@
       </c>
       <c r="E252" s="21" t="n">
         <f aca="false">E250+E249</f>
-        <v>43.6828664338562</v>
+        <v>43.6828664338563</v>
       </c>
       <c r="F252" s="21" t="n">
         <f aca="false">F250+F249</f>
-        <v>51.0884727563106</v>
+        <v>51.0884727563107</v>
       </c>
       <c r="G252" s="21" t="n">
         <f aca="false">G250+G249</f>
-        <v>55.9675301460784</v>
+        <v>55.9675301460785</v>
       </c>
       <c r="H252" s="23" t="n">
         <f aca="false">G252*(1+H253)</f>
-        <v>60.6502258875247</v>
+        <v>60.6502258875248</v>
       </c>
       <c r="I252" s="23" t="n">
         <f aca="false">H252*(1+I253)</f>
-        <v>65.0069766138119</v>
+        <v>65.006976613812</v>
       </c>
       <c r="J252" s="23" t="n">
         <f aca="false">I252*(1+J253)</f>
-        <v>68.9073952106406</v>
+        <v>68.9073952106407</v>
       </c>
       <c r="K252" s="7" t="s">
         <v>521</v>
@@ -59935,7 +59935,7 @@
       </c>
       <c r="E253" s="16" t="n">
         <f aca="false">E252/D252-1</f>
-        <v>0.553113362506443</v>
+        <v>0.553113362506445</v>
       </c>
       <c r="F253" s="16" t="n">
         <f aca="false">F252/E252-1</f>
@@ -59999,15 +59999,15 @@
       </c>
       <c r="E255" s="16" t="n">
         <f aca="false">(E245+E249)/E248</f>
-        <v>0.913596095592026</v>
+        <v>0.913596095592027</v>
       </c>
       <c r="F255" s="16" t="n">
         <f aca="false">(F245+F249)/F248</f>
-        <v>0.780246755889468</v>
+        <v>0.780246755889469</v>
       </c>
       <c r="G255" s="16" t="n">
         <f aca="false">(G245+G249)/G248</f>
-        <v>0.705633289332734</v>
+        <v>0.705633289332735</v>
       </c>
       <c r="K255" s="3" t="s">
         <v>525</v>
@@ -60022,7 +60022,7 @@
       </c>
       <c r="D256" s="20" t="n">
         <f aca="false">D250/fx/D234*1000</f>
-        <v>111.389307286659</v>
+        <v>111.38930728666</v>
       </c>
       <c r="E256" s="20" t="n">
         <f aca="false">E250/fx/E234*1000</f>
@@ -60109,7 +60109,7 @@
       </c>
       <c r="G260" s="21" t="n">
         <f aca="false">G250*G259+G249*$D$258</f>
-        <v>19.6828019910052</v>
+        <v>19.6828019910053</v>
       </c>
     </row>
     <row r="261" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -60157,11 +60157,11 @@
       </c>
       <c r="E262" s="21" t="n">
         <f aca="false">D262*(1+MAX(0,phi*E253))</f>
-        <v>2.4345282085354</v>
+        <v>2.43452820853541</v>
       </c>
       <c r="F262" s="21" t="n">
         <f aca="false">E262*(1+MAX(0,phi*F253))</f>
-        <v>2.68216522000244</v>
+        <v>2.68216522000245</v>
       </c>
       <c r="G262" s="21" t="n">
         <f aca="false">F262*(1+MAX(0,phi*G253))</f>
@@ -60188,11 +60188,11 @@
       </c>
       <c r="E263" s="21" t="n">
         <f aca="false">E262+0*E252</f>
-        <v>2.4345282085354</v>
+        <v>2.43452820853541</v>
       </c>
       <c r="F263" s="21" t="n">
         <f aca="false">F262+0*F252</f>
-        <v>2.68216522000244</v>
+        <v>2.68216522000245</v>
       </c>
       <c r="G263" s="21" t="n">
         <f aca="false">G262+0*G252</f>
@@ -60220,7 +60220,7 @@
       </c>
       <c r="F264" s="21" t="n">
         <f aca="false">F260-F263</f>
-        <v>15.5653822749008</v>
+        <v>15.5653822749009</v>
       </c>
       <c r="G264" s="21" t="n">
         <f aca="false">G260-G263</f>
@@ -60303,7 +60303,7 @@
       </c>
       <c r="G267" s="21" t="n">
         <f aca="false">(G264+G266)*nir_f</f>
-        <v>14.4329015701253</v>
+        <v>14.4329015701254</v>
       </c>
       <c r="H267" s="23" t="n">
         <f aca="false">H252*H272</f>
@@ -60442,7 +60442,7 @@
       </c>
       <c r="E271" s="16" t="n">
         <f aca="false">E270/D270-1</f>
-        <v>0.66270979919898</v>
+        <v>0.662709799198982</v>
       </c>
       <c r="F271" s="16" t="n">
         <f aca="false">F270/E270-1</f>
@@ -60450,11 +60450,11 @@
       </c>
       <c r="G271" s="16" t="n">
         <f aca="false">G270/F270-1</f>
-        <v>0.0834058662799937</v>
+        <v>0.0834058662799939</v>
       </c>
       <c r="H271" s="24" t="n">
         <f aca="false">H270/G270-1</f>
-        <v>0.0970652239026959</v>
+        <v>0.0970652239026957</v>
       </c>
       <c r="I271" s="24" t="n">
         <f aca="false">I270/H270-1</f>
@@ -60462,7 +60462,7 @@
       </c>
       <c r="J271" s="24" t="n">
         <f aca="false">J270/I270-1</f>
-        <v>0.0727883428117759</v>
+        <v>0.0727883428117755</v>
       </c>
     </row>
     <row r="272" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -60559,7 +60559,7 @@
       </c>
       <c r="D278" s="22" t="n">
         <f aca="false">itc_26*1</f>
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="E278" s="22" t="n">
         <f aca="false">itc_27*1*1</f>
@@ -60727,7 +60727,7 @@
       </c>
       <c r="D285" s="22" t="n">
         <f aca="false">D280*D284/1000</f>
-        <v>10.5297921189288</v>
+        <v>10.5297921189287</v>
       </c>
       <c r="E285" s="22" t="n">
         <f aca="false">E280*E284/1000</f>
@@ -60751,7 +60751,7 @@
       </c>
       <c r="D286" s="21" t="n">
         <f aca="false">D285*fx</f>
-        <v>70.7602030392013</v>
+        <v>70.7602030392012</v>
       </c>
       <c r="E286" s="21" t="n">
         <f aca="false">E285*fx</f>
@@ -60799,7 +60799,7 @@
       </c>
       <c r="D288" s="16" t="n">
         <f aca="false">a26_ai/D286</f>
-        <v>0.247531793970354</v>
+        <v>0.247531793970355</v>
       </c>
       <c r="K288" s="7" t="s">
         <v>510</v>
@@ -60838,19 +60838,19 @@
       </c>
       <c r="D290" s="16" t="n">
         <f aca="false">$D$288*D289</f>
-        <v>0.247531793970354</v>
+        <v>0.247531793970355</v>
       </c>
       <c r="E290" s="16" t="n">
         <f aca="false">$D$288*E289</f>
-        <v>0.247531793970354</v>
+        <v>0.247531793970355</v>
       </c>
       <c r="F290" s="16" t="n">
         <f aca="false">$D$288*F289</f>
-        <v>0.247531793970354</v>
+        <v>0.247531793970355</v>
       </c>
       <c r="G290" s="16" t="n">
         <f aca="false">$D$288*G289</f>
-        <v>0.235155204271836</v>
+        <v>0.235155204271837</v>
       </c>
     </row>
     <row r="291" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -60866,15 +60866,15 @@
       </c>
       <c r="E291" s="21" t="n">
         <f aca="false">E286*E290*E287</f>
-        <v>47.2460949055089</v>
+        <v>47.246094905509</v>
       </c>
       <c r="F291" s="21" t="n">
         <f aca="false">F286*F290*F287</f>
-        <v>67.4631212605177</v>
+        <v>67.4631212605178</v>
       </c>
       <c r="G291" s="21" t="n">
         <f aca="false">G286*G290*G287</f>
-        <v>78.3437884341354</v>
+        <v>78.3437884341355</v>
       </c>
     </row>
     <row r="292" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -61129,7 +61129,7 @@
       </c>
       <c r="E301" s="16" t="n">
         <f aca="false">(E291+E295)/E294</f>
-        <v>1.21003164134313</v>
+        <v>1.21003164134314</v>
       </c>
       <c r="F301" s="16" t="n">
         <f aca="false">(F291+F295)/F294</f>
@@ -61152,7 +61152,7 @@
       </c>
       <c r="D302" s="20" t="n">
         <f aca="false">D296/fx/D280*1000</f>
-        <v>111.389307286659</v>
+        <v>111.38930728666</v>
       </c>
       <c r="E302" s="20" t="n">
         <f aca="false">E296/fx/E280*1000</f>
@@ -61689,7 +61689,7 @@
       </c>
       <c r="D324" s="22" t="n">
         <f aca="false">itc_26*1</f>
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="E324" s="22" t="n">
         <f aca="false">itc_27*1*1</f>
@@ -61857,7 +61857,7 @@
       </c>
       <c r="D331" s="22" t="n">
         <f aca="false">D326*D330/1000</f>
-        <v>10.5297921189288</v>
+        <v>10.5297921189287</v>
       </c>
       <c r="E331" s="22" t="n">
         <f aca="false">E326*E330/1000</f>
@@ -61881,7 +61881,7 @@
       </c>
       <c r="D332" s="21" t="n">
         <f aca="false">D331*fx</f>
-        <v>70.7602030392013</v>
+        <v>70.7602030392012</v>
       </c>
       <c r="E332" s="21" t="n">
         <f aca="false">E331*fx</f>
@@ -61929,7 +61929,7 @@
       </c>
       <c r="D334" s="16" t="n">
         <f aca="false">a26_ai/D332</f>
-        <v>0.247531793970354</v>
+        <v>0.247531793970355</v>
       </c>
       <c r="K334" s="7" t="s">
         <v>510</v>
@@ -61968,7 +61968,7 @@
       </c>
       <c r="D336" s="16" t="n">
         <f aca="false">$D$334*D335</f>
-        <v>0.247531793970354</v>
+        <v>0.247531793970355</v>
       </c>
       <c r="E336" s="16" t="n">
         <f aca="false">$D$334*E335</f>
@@ -61976,7 +61976,7 @@
       </c>
       <c r="F336" s="16" t="n">
         <f aca="false">$D$334*F335</f>
-        <v>0.198025435176283</v>
+        <v>0.198025435176284</v>
       </c>
       <c r="G336" s="16" t="n">
         <f aca="false">$D$334*G335</f>
@@ -61996,15 +61996,15 @@
       </c>
       <c r="E337" s="21" t="n">
         <f aca="false">E332*E336*E333</f>
-        <v>40.3954111442101</v>
+        <v>40.3954111442102</v>
       </c>
       <c r="F337" s="21" t="n">
         <f aca="false">F332*F336*F333</f>
-        <v>50.0757188737863</v>
+        <v>50.0757188737864</v>
       </c>
       <c r="G337" s="21" t="n">
         <f aca="false">G332*G336*G333</f>
-        <v>55.928516379352</v>
+        <v>55.9285163793521</v>
       </c>
     </row>
     <row r="338" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -62112,11 +62112,11 @@
       </c>
       <c r="F342" s="21" t="n">
         <f aca="false">MIN(F337,F340-F341)</f>
-        <v>50.0757188737863</v>
+        <v>50.0757188737864</v>
       </c>
       <c r="G342" s="21" t="n">
         <f aca="false">MIN(G337,G340-G341)</f>
-        <v>55.928516379352</v>
+        <v>55.9285163793521</v>
       </c>
       <c r="K342" s="3" t="s">
         <v>519</v>
@@ -62160,23 +62160,23 @@
       </c>
       <c r="F344" s="21" t="n">
         <f aca="false">F342+F341</f>
-        <v>60.6863188737863</v>
+        <v>60.6863188737864</v>
       </c>
       <c r="G344" s="21" t="n">
         <f aca="false">G342+G341</f>
-        <v>66.539116379352</v>
+        <v>66.5391163793521</v>
       </c>
       <c r="H344" s="23" t="n">
         <f aca="false">G344*(1+H345)</f>
-        <v>72.1480730038242</v>
+        <v>72.1480730038243</v>
       </c>
       <c r="I344" s="23" t="n">
         <f aca="false">H344*(1+I345)</f>
-        <v>77.3533987676745</v>
+        <v>77.3533987676746</v>
       </c>
       <c r="J344" s="23" t="n">
         <f aca="false">I344*(1+J345)</f>
-        <v>81.994602693735</v>
+        <v>81.9946026937351</v>
       </c>
       <c r="K344" s="7" t="s">
         <v>521</v>
@@ -62199,7 +62199,7 @@
       </c>
       <c r="F345" s="16" t="n">
         <f aca="false">F344/E344-1</f>
-        <v>0.336011805208854</v>
+        <v>0.336011805208855</v>
       </c>
       <c r="G345" s="16" t="n">
         <f aca="false">G344/F344-1</f>
@@ -62263,11 +62263,11 @@
       </c>
       <c r="F347" s="16" t="n">
         <f aca="false">(F337+F341)/F340</f>
-        <v>0.998916233987175</v>
+        <v>0.998916233987177</v>
       </c>
       <c r="G347" s="16" t="n">
         <f aca="false">(G337+G341)/G340</f>
-        <v>0.927745542528538</v>
+        <v>0.927745542528539</v>
       </c>
       <c r="K347" s="3" t="s">
         <v>525</v>
@@ -62282,7 +62282,7 @@
       </c>
       <c r="D348" s="20" t="n">
         <f aca="false">D342/fx/D326*1000</f>
-        <v>111.389307286659</v>
+        <v>111.38930728666</v>
       </c>
       <c r="E348" s="20" t="n">
         <f aca="false">E342/fx/E326*1000</f>
@@ -62294,7 +62294,7 @@
       </c>
       <c r="G348" s="20" t="n">
         <f aca="false">G342/fx/G326*1000</f>
-        <v>138.3919318614</v>
+        <v>138.391931861401</v>
       </c>
     </row>
     <row r="349" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -62365,11 +62365,11 @@
       </c>
       <c r="F352" s="21" t="n">
         <f aca="false">F342*F351+F341*$D$350</f>
-        <v>19.5174120898113</v>
+        <v>19.5174120898114</v>
       </c>
       <c r="G352" s="21" t="n">
         <f aca="false">G342*G351+G341*$D$350</f>
-        <v>19.8243472012139</v>
+        <v>19.824347201214</v>
       </c>
     </row>
     <row r="353" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -62425,7 +62425,7 @@
       </c>
       <c r="G354" s="21" t="n">
         <f aca="false">F354*(1+MAX(0,phi*G345))</f>
-        <v>3.18090160010189</v>
+        <v>3.1809016001019</v>
       </c>
       <c r="K354" s="7" t="s">
         <v>532</v>
@@ -62456,7 +62456,7 @@
       </c>
       <c r="G355" s="21" t="n">
         <f aca="false">G354+0*G344</f>
-        <v>3.18090160010189</v>
+        <v>3.1809016001019</v>
       </c>
     </row>
     <row r="356" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -62484,7 +62484,7 @@
       </c>
       <c r="G356" s="21" t="n">
         <f aca="false">G352-G355</f>
-        <v>16.643445601112</v>
+        <v>16.6434456011121</v>
       </c>
     </row>
     <row r="357" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -62563,11 +62563,11 @@
       </c>
       <c r="G359" s="21" t="n">
         <f aca="false">(G356+G358)*nir_f</f>
-        <v>14.2564673361641</v>
+        <v>14.2564673361642</v>
       </c>
       <c r="H359" s="23" t="n">
         <f aca="false">H344*H364</f>
-        <v>16.7373457226104</v>
+        <v>16.7373457226105</v>
       </c>
       <c r="I359" s="23" t="n">
         <f aca="false">I344*I364</f>
@@ -62682,7 +62682,7 @@
       </c>
       <c r="I362" s="28" t="n">
         <f aca="false">I359/I361</f>
-        <v>19.6635736049722</v>
+        <v>19.6635736049723</v>
       </c>
       <c r="J362" s="28" t="n">
         <f aca="false">J359/J361</f>
@@ -62706,11 +62706,11 @@
       </c>
       <c r="F363" s="16" t="n">
         <f aca="false">F362/E362-1</f>
-        <v>0.301394182259412</v>
+        <v>0.301394182259413</v>
       </c>
       <c r="G363" s="16" t="n">
         <f aca="false">G362/F362-1</f>
-        <v>0.00815041516230108</v>
+        <v>0.00815041516230064</v>
       </c>
       <c r="H363" s="24" t="n">
         <f aca="false">H362/G362-1</f>
@@ -62819,7 +62819,7 @@
       </c>
       <c r="D370" s="22" t="n">
         <f aca="false">itc_26*1</f>
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="E370" s="22" t="n">
         <f aca="false">itc_27*1*1</f>
@@ -62987,7 +62987,7 @@
       </c>
       <c r="D377" s="22" t="n">
         <f aca="false">D372*D376/1000</f>
-        <v>10.5297921189288</v>
+        <v>10.5297921189287</v>
       </c>
       <c r="E377" s="22" t="n">
         <f aca="false">E372*E376/1000</f>
@@ -63011,7 +63011,7 @@
       </c>
       <c r="D378" s="21" t="n">
         <f aca="false">D377*fx</f>
-        <v>70.7602030392013</v>
+        <v>70.7602030392012</v>
       </c>
       <c r="E378" s="21" t="n">
         <f aca="false">E377*fx</f>
@@ -63059,7 +63059,7 @@
       </c>
       <c r="D380" s="16" t="n">
         <f aca="false">a26_ai/D378</f>
-        <v>0.247531793970354</v>
+        <v>0.247531793970355</v>
       </c>
       <c r="K380" s="7" t="s">
         <v>510</v>
@@ -63098,7 +63098,7 @@
       </c>
       <c r="D382" s="16" t="n">
         <f aca="false">$D$380*D381</f>
-        <v>0.247531793970354</v>
+        <v>0.247531793970355</v>
       </c>
       <c r="E382" s="16" t="n">
         <f aca="false">$D$380*E381</f>
@@ -63106,7 +63106,7 @@
       </c>
       <c r="F382" s="16" t="n">
         <f aca="false">$D$380*F381</f>
-        <v>0.198025435176283</v>
+        <v>0.198025435176284</v>
       </c>
       <c r="G382" s="16" t="n">
         <f aca="false">$D$380*G381</f>
@@ -63126,7 +63126,7 @@
       </c>
       <c r="E383" s="21" t="n">
         <f aca="false">E378*E382*E379</f>
-        <v>43.7971299774067</v>
+        <v>43.7971299774068</v>
       </c>
       <c r="F383" s="21" t="n">
         <f aca="false">F378*F382*F379</f>
@@ -63134,7 +63134,7 @@
       </c>
       <c r="G383" s="21" t="n">
         <f aca="false">G378*G382*G379</f>
-        <v>65.7982545639435</v>
+        <v>65.7982545639436</v>
       </c>
     </row>
     <row r="384" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -63246,7 +63246,7 @@
       </c>
       <c r="G388" s="21" t="n">
         <f aca="false">MIN(G383,G386-G387)</f>
-        <v>65.7982545639435</v>
+        <v>65.7982545639436</v>
       </c>
       <c r="K388" s="3" t="s">
         <v>519</v>
@@ -63294,19 +63294,19 @@
       </c>
       <c r="G390" s="21" t="n">
         <f aca="false">G388+G387</f>
-        <v>76.4088545639435</v>
+        <v>76.4088545639436</v>
       </c>
       <c r="H390" s="23" t="n">
         <f aca="false">G390*(1+H391)</f>
-        <v>84.7773478697718</v>
+        <v>84.7773478697719</v>
       </c>
       <c r="I390" s="23" t="n">
         <f aca="false">H390*(1+I391)</f>
-        <v>91.9631843609927</v>
+        <v>91.9631843609928</v>
       </c>
       <c r="J390" s="23" t="n">
         <f aca="false">I390*(1+J391)</f>
-        <v>97.4809754226522</v>
+        <v>97.4809754226523</v>
       </c>
       <c r="K390" s="7" t="s">
         <v>521</v>
@@ -63329,7 +63329,7 @@
       </c>
       <c r="F391" s="16" t="n">
         <f aca="false">F390/E390-1</f>
-        <v>0.367816462337267</v>
+        <v>0.367816462337269</v>
       </c>
       <c r="G391" s="16" t="n">
         <f aca="false">G390/F390-1</f>
@@ -63389,15 +63389,15 @@
       </c>
       <c r="E393" s="16" t="n">
         <f aca="false">(E383+E387)/E386</f>
-        <v>1.10475630279323</v>
+        <v>1.10475630279324</v>
       </c>
       <c r="F393" s="16" t="n">
         <f aca="false">(F383+F387)/F386</f>
-        <v>0.978368719588462</v>
+        <v>0.978368719588463</v>
       </c>
       <c r="G393" s="16" t="n">
         <f aca="false">(G383+G387)/G386</f>
-        <v>0.905554226977927</v>
+        <v>0.905554226977928</v>
       </c>
       <c r="K393" s="3" t="s">
         <v>525</v>
@@ -63412,7 +63412,7 @@
       </c>
       <c r="D394" s="20" t="n">
         <f aca="false">D388/fx/D372*1000</f>
-        <v>111.389307286659</v>
+        <v>111.38930728666</v>
       </c>
       <c r="E394" s="20" t="n">
         <f aca="false">E388/fx/E372*1000</f>
@@ -63424,7 +63424,7 @@
       </c>
       <c r="G394" s="20" t="n">
         <f aca="false">G388/fx/G372*1000</f>
-        <v>162.814037484</v>
+        <v>162.814037484001</v>
       </c>
     </row>
     <row r="395" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -63499,7 +63499,7 @@
       </c>
       <c r="G398" s="21" t="n">
         <f aca="false">G388*G397+G387*$D$396</f>
-        <v>29.9901775313432</v>
+        <v>29.9901775313433</v>
       </c>
     </row>
     <row r="399" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -63642,7 +63642,7 @@
       </c>
       <c r="G403" s="16" t="n">
         <f aca="false">G402/G390</f>
-        <v>0.346722405981896</v>
+        <v>0.346722405981897</v>
       </c>
     </row>
     <row r="404" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -63689,7 +63689,7 @@
       </c>
       <c r="F405" s="21" t="n">
         <f aca="false">(F402+F404)*nir_f</f>
-        <v>19.84647847616</v>
+        <v>19.8464784761601</v>
       </c>
       <c r="G405" s="21" t="n">
         <f aca="false">(G402+G404)*nir_f</f>
@@ -63701,7 +63701,7 @@
       </c>
       <c r="I405" s="23" t="n">
         <f aca="false">I390*I410</f>
-        <v>25.5420829244541</v>
+        <v>25.5420829244542</v>
       </c>
       <c r="J405" s="23" t="n">
         <f aca="false">J390*J410</f>
@@ -63836,7 +63836,7 @@
       </c>
       <c r="F409" s="16" t="n">
         <f aca="false">F408/E408-1</f>
-        <v>0.456541251072616</v>
+        <v>0.456541251072618</v>
       </c>
       <c r="G409" s="16" t="n">
         <f aca="false">G408/F408-1</f>
@@ -63844,7 +63844,7 @@
       </c>
       <c r="H409" s="24" t="n">
         <f aca="false">H408/G408-1</f>
-        <v>0.0712234143235466</v>
+        <v>0.0712234143235464</v>
       </c>
       <c r="I409" s="24" t="n">
         <f aca="false">I408/H408-1</f>
@@ -63852,7 +63852,7 @@
       </c>
       <c r="J409" s="24" t="n">
         <f aca="false">J408/I408-1</f>
-        <v>0.0206969311387522</v>
+        <v>0.0206969311387519</v>
       </c>
     </row>
     <row r="410" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -63880,7 +63880,7 @@
       </c>
       <c r="G410" s="16" t="n">
         <f aca="false">G405/G390</f>
-        <v>0.298338955492667</v>
+        <v>0.298338955492668</v>
       </c>
       <c r="H410" s="24" t="n">
         <f aca="false">$G410+(fade_mA-$G410)*1/3</f>
@@ -63949,7 +63949,7 @@
       </c>
       <c r="D416" s="22" t="n">
         <f aca="false">itc_26*1</f>
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="E416" s="22" t="n">
         <f aca="false">itc_27*1*1</f>
@@ -64117,7 +64117,7 @@
       </c>
       <c r="D423" s="22" t="n">
         <f aca="false">D418*D422/1000</f>
-        <v>10.5297921189288</v>
+        <v>10.5297921189287</v>
       </c>
       <c r="E423" s="22" t="n">
         <f aca="false">E418*E422/1000</f>
@@ -64141,7 +64141,7 @@
       </c>
       <c r="D424" s="21" t="n">
         <f aca="false">D423*fx</f>
-        <v>70.7602030392013</v>
+        <v>70.7602030392012</v>
       </c>
       <c r="E424" s="21" t="n">
         <f aca="false">E423*fx</f>
@@ -64189,7 +64189,7 @@
       </c>
       <c r="D426" s="16" t="n">
         <f aca="false">a26_ai/D424</f>
-        <v>0.247531793970354</v>
+        <v>0.247531793970355</v>
       </c>
       <c r="K426" s="7" t="s">
         <v>510</v>
@@ -64228,7 +64228,7 @@
       </c>
       <c r="D428" s="16" t="n">
         <f aca="false">$D$426*D427</f>
-        <v>0.247531793970354</v>
+        <v>0.247531793970355</v>
       </c>
       <c r="E428" s="16" t="n">
         <f aca="false">$D$426*E427</f>
@@ -64236,7 +64236,7 @@
       </c>
       <c r="F428" s="16" t="n">
         <f aca="false">$D$426*F427</f>
-        <v>0.198025435176283</v>
+        <v>0.198025435176284</v>
       </c>
       <c r="G428" s="16" t="n">
         <f aca="false">$D$426*G427</f>
@@ -64256,15 +64256,15 @@
       </c>
       <c r="E429" s="21" t="n">
         <f aca="false">E424*E428*E425</f>
-        <v>42.521485414958</v>
+        <v>42.5214854149581</v>
       </c>
       <c r="F429" s="21" t="n">
         <f aca="false">F424*F428*F425</f>
-        <v>53.9704970084141</v>
+        <v>53.9704970084142</v>
       </c>
       <c r="G429" s="21" t="n">
         <f aca="false">G424*G428*G425</f>
-        <v>61.8503592901069</v>
+        <v>61.850359290107</v>
       </c>
     </row>
     <row r="430" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -64527,7 +64527,7 @@
       </c>
       <c r="G439" s="16" t="n">
         <f aca="false">(G429+G433)/G432</f>
-        <v>1.14197609128518</v>
+        <v>1.14197609128519</v>
       </c>
       <c r="K439" s="3" t="s">
         <v>525</v>
@@ -64542,7 +64542,7 @@
       </c>
       <c r="D440" s="20" t="n">
         <f aca="false">D434/fx/D418*1000</f>
-        <v>111.389307286659</v>
+        <v>111.38930728666</v>
       </c>
       <c r="E440" s="20" t="n">
         <f aca="false">E434/fx/E418*1000</f>
@@ -65079,7 +65079,7 @@
       </c>
       <c r="D462" s="22" t="n">
         <f aca="false">itc_26*1</f>
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="E462" s="22" t="n">
         <f aca="false">itc_27*1*1</f>
@@ -65247,7 +65247,7 @@
       </c>
       <c r="D469" s="22" t="n">
         <f aca="false">D464*D468/1000</f>
-        <v>10.5297921189288</v>
+        <v>10.5297921189287</v>
       </c>
       <c r="E469" s="22" t="n">
         <f aca="false">E464*E468/1000</f>
@@ -65271,7 +65271,7 @@
       </c>
       <c r="D470" s="21" t="n">
         <f aca="false">D469*fx</f>
-        <v>70.7602030392013</v>
+        <v>70.7602030392012</v>
       </c>
       <c r="E470" s="21" t="n">
         <f aca="false">E469*fx</f>
@@ -65319,7 +65319,7 @@
       </c>
       <c r="D472" s="16" t="n">
         <f aca="false">a26_ai/D470</f>
-        <v>0.247531793970354</v>
+        <v>0.247531793970355</v>
       </c>
       <c r="K472" s="7" t="s">
         <v>510</v>
@@ -65358,7 +65358,7 @@
       </c>
       <c r="D474" s="16" t="n">
         <f aca="false">$D$472*D473</f>
-        <v>0.247531793970354</v>
+        <v>0.247531793970355</v>
       </c>
       <c r="E474" s="16" t="n">
         <f aca="false">$D$472*E473</f>
@@ -65366,7 +65366,7 @@
       </c>
       <c r="F474" s="16" t="n">
         <f aca="false">$D$472*F473</f>
-        <v>0.198025435176283</v>
+        <v>0.198025435176284</v>
       </c>
       <c r="G474" s="16" t="n">
         <f aca="false">$D$472*G473</f>
@@ -65386,15 +65386,15 @@
       </c>
       <c r="E475" s="21" t="n">
         <f aca="false">E470*E474*E471</f>
-        <v>42.521485414958</v>
+        <v>42.5214854149581</v>
       </c>
       <c r="F475" s="21" t="n">
         <f aca="false">F470*F474*F471</f>
-        <v>53.9704970084141</v>
+        <v>53.9704970084142</v>
       </c>
       <c r="G475" s="21" t="n">
         <f aca="false">G470*G474*G471</f>
-        <v>61.8503592901069</v>
+        <v>61.850359290107</v>
       </c>
     </row>
     <row r="476" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -65498,15 +65498,15 @@
       </c>
       <c r="E480" s="21" t="n">
         <f aca="false">MIN(E475,E478-E479)</f>
-        <v>42.521485414958</v>
+        <v>42.5214854149581</v>
       </c>
       <c r="F480" s="21" t="n">
         <f aca="false">MIN(F475,F478-F479)</f>
-        <v>53.9704970084141</v>
+        <v>53.9704970084142</v>
       </c>
       <c r="G480" s="21" t="n">
         <f aca="false">MIN(G475,G478-G479)</f>
-        <v>61.8503592901069</v>
+        <v>61.850359290107</v>
       </c>
       <c r="K480" s="3" t="s">
         <v>519</v>
@@ -65546,15 +65546,15 @@
       </c>
       <c r="E482" s="21" t="n">
         <f aca="false">E480+E479</f>
-        <v>53.132085414958</v>
+        <v>53.1320854149581</v>
       </c>
       <c r="F482" s="21" t="n">
         <f aca="false">F480+F479</f>
-        <v>64.5810970084141</v>
+        <v>64.5810970084142</v>
       </c>
       <c r="G482" s="21" t="n">
         <f aca="false">G480+G479</f>
-        <v>72.4609592901069</v>
+        <v>72.460959290107</v>
       </c>
       <c r="H482" s="23" t="n">
         <f aca="false">G482*(1+H483)</f>
@@ -65562,11 +65562,11 @@
       </c>
       <c r="I482" s="23" t="n">
         <f aca="false">H482*(1+I483)</f>
-        <v>86.2423476187718</v>
+        <v>86.2423476187719</v>
       </c>
       <c r="J482" s="23" t="n">
         <f aca="false">I482*(1+J483)</f>
-        <v>91.4168884758982</v>
+        <v>91.4168884758983</v>
       </c>
       <c r="K482" s="7" t="s">
         <v>521</v>
@@ -65585,7 +65585,7 @@
       </c>
       <c r="E483" s="16" t="n">
         <f aca="false">E482/D482-1</f>
-        <v>0.889073647691033</v>
+        <v>0.889073647691036</v>
       </c>
       <c r="F483" s="16" t="n">
         <f aca="false">F482/E482-1</f>
@@ -65649,15 +65649,15 @@
       </c>
       <c r="E485" s="16" t="n">
         <f aca="false">(E475+E479)/E478</f>
-        <v>0.994249288258439</v>
+        <v>0.99424928825844</v>
       </c>
       <c r="F485" s="16" t="n">
         <f aca="false">(F475+F479)/F478</f>
-        <v>0.845410582533425</v>
+        <v>0.845410582533426</v>
       </c>
       <c r="G485" s="16" t="n">
         <f aca="false">(G475+G479)/G478</f>
-        <v>0.806100770318954</v>
+        <v>0.806100770318955</v>
       </c>
       <c r="K485" s="3" t="s">
         <v>525</v>
@@ -65672,11 +65672,11 @@
       </c>
       <c r="D486" s="20" t="n">
         <f aca="false">D480/fx/D464*1000</f>
-        <v>111.389307286659</v>
+        <v>111.38930728666</v>
       </c>
       <c r="E486" s="20" t="n">
         <f aca="false">E480/fx/E464*1000</f>
-        <v>151.935015139003</v>
+        <v>151.935015139004</v>
       </c>
       <c r="F486" s="20" t="n">
         <f aca="false">F480/fx/F464*1000</f>
@@ -65684,7 +65684,7 @@
       </c>
       <c r="G486" s="20" t="n">
         <f aca="false">G480/fx/G464*1000</f>
-        <v>153.04519523496</v>
+        <v>153.045195234961</v>
       </c>
     </row>
     <row r="487" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -65874,7 +65874,7 @@
       </c>
       <c r="G494" s="21" t="n">
         <f aca="false">G490-G493</f>
-        <v>22.5267238201755</v>
+        <v>22.5267238201756</v>
       </c>
     </row>
     <row r="495" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -65965,7 +65965,7 @@
       </c>
       <c r="J497" s="23" t="n">
         <f aca="false">J482*J502</f>
-        <v>24.4489205143475</v>
+        <v>24.4489205143476</v>
       </c>
     </row>
     <row r="498" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -66096,11 +66096,11 @@
       </c>
       <c r="F501" s="16" t="n">
         <f aca="false">F500/E500-1</f>
-        <v>0.225703796092433</v>
+        <v>0.225703796092434</v>
       </c>
       <c r="G501" s="16" t="n">
         <f aca="false">G500/F500-1</f>
-        <v>0.109419018825979</v>
+        <v>0.109419018825978</v>
       </c>
       <c r="H501" s="24" t="n">
         <f aca="false">H500/G500-1</f>
@@ -66108,11 +66108,11 @@
       </c>
       <c r="I501" s="24" t="n">
         <f aca="false">I500/H500-1</f>
-        <v>0.0810808544534336</v>
+        <v>0.0810808544534338</v>
       </c>
       <c r="J501" s="24" t="n">
         <f aca="false">J500/I500-1</f>
-        <v>0.0604012100743843</v>
+        <v>0.060401210074384</v>
       </c>
     </row>
     <row r="502" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -66209,7 +66209,7 @@
       </c>
       <c r="D508" s="22" t="n">
         <f aca="false">itc_26*1</f>
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="E508" s="22" t="n">
         <f aca="false">itc_27*1*1</f>
@@ -66377,7 +66377,7 @@
       </c>
       <c r="D515" s="22" t="n">
         <f aca="false">D510*D514/1000</f>
-        <v>10.5297921189288</v>
+        <v>10.5297921189287</v>
       </c>
       <c r="E515" s="22" t="n">
         <f aca="false">E510*E514/1000</f>
@@ -66401,7 +66401,7 @@
       </c>
       <c r="D516" s="21" t="n">
         <f aca="false">D515*fx</f>
-        <v>70.7602030392013</v>
+        <v>70.7602030392012</v>
       </c>
       <c r="E516" s="21" t="n">
         <f aca="false">E515*fx</f>
@@ -66449,7 +66449,7 @@
       </c>
       <c r="D518" s="16" t="n">
         <f aca="false">a26_ai/D516</f>
-        <v>0.247531793970354</v>
+        <v>0.247531793970355</v>
       </c>
       <c r="K518" s="7" t="s">
         <v>510</v>
@@ -66488,7 +66488,7 @@
       </c>
       <c r="D520" s="16" t="n">
         <f aca="false">$D$518*D519</f>
-        <v>0.247531793970354</v>
+        <v>0.247531793970355</v>
       </c>
       <c r="E520" s="16" t="n">
         <f aca="false">$D$518*E519</f>
@@ -66496,7 +66496,7 @@
       </c>
       <c r="F520" s="16" t="n">
         <f aca="false">$D$518*F519</f>
-        <v>0.198025435176283</v>
+        <v>0.198025435176284</v>
       </c>
       <c r="G520" s="16" t="n">
         <f aca="false">$D$518*G519</f>
@@ -66516,15 +66516,15 @@
       </c>
       <c r="E521" s="21" t="n">
         <f aca="false">E516*E520*E517</f>
-        <v>42.521485414958</v>
+        <v>42.5214854149581</v>
       </c>
       <c r="F521" s="21" t="n">
         <f aca="false">F516*F520*F517</f>
-        <v>53.9704970084141</v>
+        <v>53.9704970084142</v>
       </c>
       <c r="G521" s="21" t="n">
         <f aca="false">G516*G520*G517</f>
-        <v>61.8503592901069</v>
+        <v>61.850359290107</v>
       </c>
     </row>
     <row r="522" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -66632,11 +66632,11 @@
       </c>
       <c r="F526" s="21" t="n">
         <f aca="false">MIN(F521,F524-F525)</f>
-        <v>53.9704970084141</v>
+        <v>53.9704970084142</v>
       </c>
       <c r="G526" s="21" t="n">
         <f aca="false">MIN(G521,G524-G525)</f>
-        <v>61.8503592901069</v>
+        <v>61.850359290107</v>
       </c>
       <c r="K526" s="3" t="s">
         <v>519</v>
@@ -66680,11 +66680,11 @@
       </c>
       <c r="F528" s="21" t="n">
         <f aca="false">F526+F525</f>
-        <v>64.5810970084141</v>
+        <v>64.5810970084142</v>
       </c>
       <c r="G528" s="21" t="n">
         <f aca="false">G526+G525</f>
-        <v>72.4609592901069</v>
+        <v>72.460959290107</v>
       </c>
       <c r="H528" s="23" t="n">
         <f aca="false">G528*(1+H529)</f>
@@ -66692,11 +66692,11 @@
       </c>
       <c r="I528" s="23" t="n">
         <f aca="false">H528*(1+I529)</f>
-        <v>86.2423476187718</v>
+        <v>86.2423476187719</v>
       </c>
       <c r="J528" s="23" t="n">
         <f aca="false">I528*(1+J529)</f>
-        <v>91.4168884758982</v>
+        <v>91.4168884758983</v>
       </c>
       <c r="K528" s="7" t="s">
         <v>521</v>
@@ -66719,7 +66719,7 @@
       </c>
       <c r="F529" s="16" t="n">
         <f aca="false">F528/E528-1</f>
-        <v>0.350667730682813</v>
+        <v>0.350667730682815</v>
       </c>
       <c r="G529" s="16" t="n">
         <f aca="false">G528/F528-1</f>
@@ -66783,11 +66783,11 @@
       </c>
       <c r="F531" s="16" t="n">
         <f aca="false">(F521+F525)/F524</f>
-        <v>0.986312346288996</v>
+        <v>0.986312346288997</v>
       </c>
       <c r="G531" s="16" t="n">
         <f aca="false">(G521+G525)/G524</f>
-        <v>0.913580873028148</v>
+        <v>0.913580873028149</v>
       </c>
       <c r="K531" s="3" t="s">
         <v>525</v>
@@ -66802,7 +66802,7 @@
       </c>
       <c r="D532" s="20" t="n">
         <f aca="false">D526/fx/D510*1000</f>
-        <v>111.389307286659</v>
+        <v>111.38930728666</v>
       </c>
       <c r="E532" s="20" t="n">
         <f aca="false">E526/fx/E510*1000</f>
@@ -66814,7 +66814,7 @@
       </c>
       <c r="G532" s="20" t="n">
         <f aca="false">G526/fx/G510*1000</f>
-        <v>153.04519523496</v>
+        <v>153.045195234961</v>
       </c>
     </row>
     <row r="533" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -67095,7 +67095,7 @@
       </c>
       <c r="J543" s="23" t="n">
         <f aca="false">J528*J548</f>
-        <v>24.4489205143475</v>
+        <v>24.4489205143476</v>
       </c>
     </row>
     <row r="544" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -67202,7 +67202,7 @@
       </c>
       <c r="I546" s="28" t="n">
         <f aca="false">I543/I545</f>
-        <v>22.6133974416049</v>
+        <v>22.613397441605</v>
       </c>
       <c r="J546" s="28" t="n">
         <f aca="false">J543/J545</f>
@@ -67226,11 +67226,11 @@
       </c>
       <c r="F547" s="16" t="n">
         <f aca="false">F546/E546-1</f>
-        <v>0.345782113578253</v>
+        <v>0.345782113578254</v>
       </c>
       <c r="G547" s="16" t="n">
         <f aca="false">G546/F546-1</f>
-        <v>0.0727961414801028</v>
+        <v>0.0727961414801024</v>
       </c>
       <c r="H547" s="24" t="n">
         <f aca="false">H546/G546-1</f>
@@ -67242,7 +67242,7 @@
       </c>
       <c r="J547" s="24" t="n">
         <f aca="false">J546/I546-1</f>
-        <v>0.100606426581834</v>
+        <v>0.100606426581833</v>
       </c>
     </row>
     <row r="548" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -67339,7 +67339,7 @@
       </c>
       <c r="D554" s="22" t="n">
         <f aca="false">itc_26*1</f>
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="E554" s="22" t="n">
         <f aca="false">itc_27*1*1</f>
@@ -67507,7 +67507,7 @@
       </c>
       <c r="D561" s="22" t="n">
         <f aca="false">D556*D560/1000</f>
-        <v>10.5297921189288</v>
+        <v>10.5297921189287</v>
       </c>
       <c r="E561" s="22" t="n">
         <f aca="false">E556*E560/1000</f>
@@ -67531,7 +67531,7 @@
       </c>
       <c r="D562" s="21" t="n">
         <f aca="false">D561*fx</f>
-        <v>70.7602030392013</v>
+        <v>70.7602030392012</v>
       </c>
       <c r="E562" s="21" t="n">
         <f aca="false">E561*fx</f>
@@ -67579,7 +67579,7 @@
       </c>
       <c r="D564" s="16" t="n">
         <f aca="false">a26_ai/D562</f>
-        <v>0.247531793970354</v>
+        <v>0.247531793970355</v>
       </c>
       <c r="K564" s="7" t="s">
         <v>510</v>
@@ -67618,7 +67618,7 @@
       </c>
       <c r="D566" s="16" t="n">
         <f aca="false">$D$564*D565</f>
-        <v>0.247531793970354</v>
+        <v>0.247531793970355</v>
       </c>
       <c r="E566" s="16" t="n">
         <f aca="false">$D$564*E565</f>
@@ -67626,7 +67626,7 @@
       </c>
       <c r="F566" s="16" t="n">
         <f aca="false">$D$564*F565</f>
-        <v>0.198025435176283</v>
+        <v>0.198025435176284</v>
       </c>
       <c r="G566" s="16" t="n">
         <f aca="false">$D$564*G565</f>
@@ -67646,15 +67646,15 @@
       </c>
       <c r="E567" s="21" t="n">
         <f aca="false">E562*E566*E563</f>
-        <v>42.521485414958</v>
+        <v>42.5214854149581</v>
       </c>
       <c r="F567" s="21" t="n">
         <f aca="false">F562*F566*F563</f>
-        <v>53.9704970084141</v>
+        <v>53.9704970084142</v>
       </c>
       <c r="G567" s="21" t="n">
         <f aca="false">G562*G566*G563</f>
-        <v>61.8503592901069</v>
+        <v>61.850359290107</v>
       </c>
     </row>
     <row r="568" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -67762,11 +67762,11 @@
       </c>
       <c r="F572" s="21" t="n">
         <f aca="false">MIN(F567,F570-F571)</f>
-        <v>53.9704970084141</v>
+        <v>53.9704970084142</v>
       </c>
       <c r="G572" s="21" t="n">
         <f aca="false">MIN(G567,G570-G571)</f>
-        <v>61.8503592901069</v>
+        <v>61.850359290107</v>
       </c>
       <c r="K572" s="3" t="s">
         <v>519</v>
@@ -67810,11 +67810,11 @@
       </c>
       <c r="F574" s="21" t="n">
         <f aca="false">F572+F571</f>
-        <v>64.5810970084141</v>
+        <v>64.5810970084142</v>
       </c>
       <c r="G574" s="21" t="n">
         <f aca="false">G572+G571</f>
-        <v>72.4609592901069</v>
+        <v>72.460959290107</v>
       </c>
       <c r="H574" s="23" t="n">
         <f aca="false">G574*(1+H575)</f>
@@ -67822,11 +67822,11 @@
       </c>
       <c r="I574" s="23" t="n">
         <f aca="false">H574*(1+I575)</f>
-        <v>86.2423476187718</v>
+        <v>86.2423476187719</v>
       </c>
       <c r="J574" s="23" t="n">
         <f aca="false">I574*(1+J575)</f>
-        <v>91.4168884758982</v>
+        <v>91.4168884758983</v>
       </c>
       <c r="K574" s="7" t="s">
         <v>521</v>
@@ -67849,7 +67849,7 @@
       </c>
       <c r="F575" s="16" t="n">
         <f aca="false">F574/E574-1</f>
-        <v>0.350667730682813</v>
+        <v>0.350667730682815</v>
       </c>
       <c r="G575" s="16" t="n">
         <f aca="false">G574/F574-1</f>
@@ -67913,11 +67913,11 @@
       </c>
       <c r="F577" s="16" t="n">
         <f aca="false">(F567+F571)/F570</f>
-        <v>0.986312346288996</v>
+        <v>0.986312346288997</v>
       </c>
       <c r="G577" s="16" t="n">
         <f aca="false">(G567+G571)/G570</f>
-        <v>0.913580873028148</v>
+        <v>0.913580873028149</v>
       </c>
       <c r="K577" s="3" t="s">
         <v>525</v>
@@ -67932,7 +67932,7 @@
       </c>
       <c r="D578" s="20" t="n">
         <f aca="false">D572/fx/D556*1000</f>
-        <v>111.389307286659</v>
+        <v>111.38930728666</v>
       </c>
       <c r="E578" s="20" t="n">
         <f aca="false">E572/fx/E556*1000</f>
@@ -67944,7 +67944,7 @@
       </c>
       <c r="G578" s="20" t="n">
         <f aca="false">G572/fx/G556*1000</f>
-        <v>153.04519523496</v>
+        <v>153.045195234961</v>
       </c>
     </row>
     <row r="579" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -68019,7 +68019,7 @@
       </c>
       <c r="G582" s="21" t="n">
         <f aca="false">G572*G581+G571*$D$580</f>
-        <v>27.1608525850936</v>
+        <v>27.1608525850937</v>
       </c>
     </row>
     <row r="583" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -68134,7 +68134,7 @@
       </c>
       <c r="G586" s="21" t="n">
         <f aca="false">G582-G585</f>
-        <v>23.7891022115819</v>
+        <v>23.789102211582</v>
       </c>
     </row>
     <row r="587" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -68213,7 +68213,7 @@
       </c>
       <c r="G589" s="21" t="n">
         <f aca="false">(G586+G588)*nir_f</f>
-        <v>20.4517516174415</v>
+        <v>20.4517516174416</v>
       </c>
       <c r="H589" s="23" t="n">
         <f aca="false">H574*H594</f>
@@ -68225,7 +68225,7 @@
       </c>
       <c r="J589" s="23" t="n">
         <f aca="false">J574*J594</f>
-        <v>24.4489205143475</v>
+        <v>24.4489205143476</v>
       </c>
     </row>
     <row r="590" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -68356,7 +68356,7 @@
       </c>
       <c r="F593" s="16" t="n">
         <f aca="false">F592/E592-1</f>
-        <v>0.391389342264954</v>
+        <v>0.391389342264955</v>
       </c>
       <c r="G593" s="16" t="n">
         <f aca="false">G592/F592-1</f>
@@ -68364,15 +68364,15 @@
       </c>
       <c r="H593" s="24" t="n">
         <f aca="false">H592/G592-1</f>
-        <v>0.0820919321454501</v>
+        <v>0.0820919321454499</v>
       </c>
       <c r="I593" s="24" t="n">
         <f aca="false">I592/H592-1</f>
-        <v>0.0614455347090455</v>
+        <v>0.0614455347090452</v>
       </c>
       <c r="J593" s="24" t="n">
         <f aca="false">J592/I592-1</f>
-        <v>0.0408000526333105</v>
+        <v>0.0408000526333103</v>
       </c>
     </row>
     <row r="594" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -68469,7 +68469,7 @@
       </c>
       <c r="D600" s="22" t="n">
         <f aca="false">itc_26*1</f>
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="E600" s="22" t="n">
         <f aca="false">itc_27*1*mf_lo</f>
@@ -68637,7 +68637,7 @@
       </c>
       <c r="D607" s="22" t="n">
         <f aca="false">D602*D606/1000</f>
-        <v>10.5297921189288</v>
+        <v>10.5297921189287</v>
       </c>
       <c r="E607" s="22" t="n">
         <f aca="false">E602*E606/1000</f>
@@ -68661,7 +68661,7 @@
       </c>
       <c r="D608" s="21" t="n">
         <f aca="false">D607*fx</f>
-        <v>70.7602030392013</v>
+        <v>70.7602030392012</v>
       </c>
       <c r="E608" s="21" t="n">
         <f aca="false">E607*fx</f>
@@ -68709,7 +68709,7 @@
       </c>
       <c r="D610" s="16" t="n">
         <f aca="false">a26_ai/D608</f>
-        <v>0.247531793970354</v>
+        <v>0.247531793970355</v>
       </c>
       <c r="K610" s="7" t="s">
         <v>510</v>
@@ -68748,7 +68748,7 @@
       </c>
       <c r="D612" s="16" t="n">
         <f aca="false">$D$610*D611</f>
-        <v>0.247531793970354</v>
+        <v>0.247531793970355</v>
       </c>
       <c r="E612" s="16" t="n">
         <f aca="false">$D$610*E611</f>
@@ -68756,7 +68756,7 @@
       </c>
       <c r="F612" s="16" t="n">
         <f aca="false">$D$610*F611</f>
-        <v>0.198025435176283</v>
+        <v>0.198025435176284</v>
       </c>
       <c r="G612" s="16" t="n">
         <f aca="false">$D$610*G611</f>
@@ -68776,11 +68776,11 @@
       </c>
       <c r="E613" s="21" t="n">
         <f aca="false">E608*E612*E609</f>
-        <v>34.0171883319664</v>
+        <v>34.0171883319665</v>
       </c>
       <c r="F613" s="21" t="n">
         <f aca="false">F608*F612*F609</f>
-        <v>43.1763976067313</v>
+        <v>43.1763976067314</v>
       </c>
       <c r="G613" s="21" t="n">
         <f aca="false">G608*G612*G609</f>
@@ -68888,11 +68888,11 @@
       </c>
       <c r="E618" s="21" t="n">
         <f aca="false">MIN(E613,E616-E617)</f>
-        <v>34.0171883319664</v>
+        <v>34.0171883319665</v>
       </c>
       <c r="F618" s="21" t="n">
         <f aca="false">MIN(F613,F616-F617)</f>
-        <v>43.1763976067313</v>
+        <v>43.1763976067314</v>
       </c>
       <c r="G618" s="21" t="n">
         <f aca="false">MIN(G613,G616-G617)</f>
@@ -68936,11 +68936,11 @@
       </c>
       <c r="E620" s="21" t="n">
         <f aca="false">E618+E617</f>
-        <v>44.6277883319664</v>
+        <v>44.6277883319665</v>
       </c>
       <c r="F620" s="21" t="n">
         <f aca="false">F618+F617</f>
-        <v>53.7869976067313</v>
+        <v>53.7869976067314</v>
       </c>
       <c r="G620" s="21" t="n">
         <f aca="false">G618+G617</f>
@@ -68956,7 +68956,7 @@
       </c>
       <c r="J620" s="23" t="n">
         <f aca="false">I620*(1+J621)</f>
-        <v>75.4776259992125</v>
+        <v>75.4776259992126</v>
       </c>
       <c r="K620" s="7" t="s">
         <v>521</v>
@@ -68975,7 +68975,7 @@
       </c>
       <c r="E621" s="16" t="n">
         <f aca="false">E620/D620-1</f>
-        <v>0.586709391024902</v>
+        <v>0.586709391024904</v>
       </c>
       <c r="F621" s="16" t="n">
         <f aca="false">F620/E620-1</f>
@@ -69039,7 +69039,7 @@
       </c>
       <c r="E623" s="16" t="n">
         <f aca="false">(E613+E617)/E616</f>
-        <v>0.933358465308766</v>
+        <v>0.933358465308767</v>
       </c>
       <c r="F623" s="16" t="n">
         <f aca="false">(F613+F617)/F616</f>
@@ -69047,7 +69047,7 @@
       </c>
       <c r="G623" s="16" t="n">
         <f aca="false">(G613+G617)/G616</f>
-        <v>0.757620185256588</v>
+        <v>0.757620185256589</v>
       </c>
       <c r="K623" s="3" t="s">
         <v>525</v>
@@ -69062,11 +69062,11 @@
       </c>
       <c r="D624" s="20" t="n">
         <f aca="false">D618/fx/D602*1000</f>
-        <v>111.389307286659</v>
+        <v>111.38930728666</v>
       </c>
       <c r="E624" s="20" t="n">
         <f aca="false">E618/fx/E602*1000</f>
-        <v>151.935015139003</v>
+        <v>151.935015139004</v>
       </c>
       <c r="F624" s="20" t="n">
         <f aca="false">F618/fx/F602*1000</f>
@@ -69074,7 +69074,7 @@
       </c>
       <c r="G624" s="20" t="n">
         <f aca="false">G618/fx/G602*1000</f>
-        <v>153.04519523496</v>
+        <v>153.045195234961</v>
       </c>
     </row>
     <row r="625" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -69197,7 +69197,7 @@
       </c>
       <c r="E630" s="21" t="n">
         <f aca="false">D630*(1+MAX(0,phi*E621))</f>
-        <v>2.47137441764082</v>
+        <v>2.47137441764083</v>
       </c>
       <c r="F630" s="21" t="n">
         <f aca="false">E630*(1+MAX(0,phi*F621))</f>
@@ -69205,7 +69205,7 @@
       </c>
       <c r="G630" s="21" t="n">
         <f aca="false">F630*(1+MAX(0,phi*G621))</f>
-        <v>2.97089185169489</v>
+        <v>2.9708918516949</v>
       </c>
       <c r="K630" s="7" t="s">
         <v>532</v>
@@ -69228,7 +69228,7 @@
       </c>
       <c r="E631" s="21" t="n">
         <f aca="false">E630+0*E620</f>
-        <v>2.47137441764082</v>
+        <v>2.47137441764083</v>
       </c>
       <c r="F631" s="21" t="n">
         <f aca="false">F630+0*F620</f>
@@ -69236,7 +69236,7 @@
       </c>
       <c r="G631" s="21" t="n">
         <f aca="false">G630+0*G620</f>
-        <v>2.97089185169489</v>
+        <v>2.9708918516949</v>
       </c>
     </row>
     <row r="632" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -69256,7 +69256,7 @@
       </c>
       <c r="E632" s="21" t="n">
         <f aca="false">E628-E631</f>
-        <v>13.5701184347028</v>
+        <v>13.5701184347029</v>
       </c>
       <c r="F632" s="21" t="n">
         <f aca="false">F628-F631</f>
@@ -69351,7 +69351,7 @@
       </c>
       <c r="I635" s="23" t="n">
         <f aca="false">I620*I640</f>
-        <v>18.8845109948697</v>
+        <v>18.8845109948698</v>
       </c>
       <c r="J635" s="23" t="n">
         <f aca="false">J620*J640</f>
@@ -69482,7 +69482,7 @@
       </c>
       <c r="E639" s="16" t="n">
         <f aca="false">E638/D638-1</f>
-        <v>0.705932238187216</v>
+        <v>0.705932238187219</v>
       </c>
       <c r="F639" s="16" t="n">
         <f aca="false">F638/E638-1</f>
@@ -69498,7 +69498,7 @@
       </c>
       <c r="I639" s="24" t="n">
         <f aca="false">I638/H638-1</f>
-        <v>0.0882258841504762</v>
+        <v>0.0882258841504757</v>
       </c>
       <c r="J639" s="24" t="n">
         <f aca="false">J638/I638-1</f>
@@ -69599,7 +69599,7 @@
       </c>
       <c r="D646" s="22" t="n">
         <f aca="false">itc_26*1</f>
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="E646" s="22" t="n">
         <f aca="false">itc_27*1*mf_hi</f>
@@ -69767,7 +69767,7 @@
       </c>
       <c r="D653" s="22" t="n">
         <f aca="false">D648*D652/1000</f>
-        <v>10.5297921189288</v>
+        <v>10.5297921189287</v>
       </c>
       <c r="E653" s="22" t="n">
         <f aca="false">E648*E652/1000</f>
@@ -69791,7 +69791,7 @@
       </c>
       <c r="D654" s="21" t="n">
         <f aca="false">D653*fx</f>
-        <v>70.7602030392013</v>
+        <v>70.7602030392012</v>
       </c>
       <c r="E654" s="21" t="n">
         <f aca="false">E653*fx</f>
@@ -69839,7 +69839,7 @@
       </c>
       <c r="D656" s="16" t="n">
         <f aca="false">a26_ai/D654</f>
-        <v>0.247531793970354</v>
+        <v>0.247531793970355</v>
       </c>
       <c r="K656" s="7" t="s">
         <v>510</v>
@@ -69878,7 +69878,7 @@
       </c>
       <c r="D658" s="16" t="n">
         <f aca="false">$D$656*D657</f>
-        <v>0.247531793970354</v>
+        <v>0.247531793970355</v>
       </c>
       <c r="E658" s="16" t="n">
         <f aca="false">$D$656*E657</f>
@@ -69886,7 +69886,7 @@
       </c>
       <c r="F658" s="16" t="n">
         <f aca="false">$D$656*F657</f>
-        <v>0.198025435176283</v>
+        <v>0.198025435176284</v>
       </c>
       <c r="G658" s="16" t="n">
         <f aca="false">$D$656*G657</f>
@@ -69906,15 +69906,15 @@
       </c>
       <c r="E659" s="21" t="n">
         <f aca="false">E654*E658*E655</f>
-        <v>51.0257824979496</v>
+        <v>51.0257824979497</v>
       </c>
       <c r="F659" s="21" t="n">
         <f aca="false">F654*F658*F655</f>
-        <v>64.764596410097</v>
+        <v>64.7645964100971</v>
       </c>
       <c r="G659" s="21" t="n">
         <f aca="false">G654*G658*G655</f>
-        <v>74.2204311481283</v>
+        <v>74.2204311481284</v>
       </c>
     </row>
     <row r="660" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -70192,7 +70192,7 @@
       </c>
       <c r="D670" s="20" t="n">
         <f aca="false">D664/fx/D648*1000</f>
-        <v>111.389307286659</v>
+        <v>111.38930728666</v>
       </c>
       <c r="E670" s="20" t="n">
         <f aca="false">E664/fx/E648*1000</f>
@@ -70729,7 +70729,7 @@
       </c>
       <c r="D692" s="22" t="n">
         <f aca="false">itc_26*1</f>
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="E692" s="22" t="n">
         <f aca="false">itc_27*1*1</f>
@@ -70897,7 +70897,7 @@
       </c>
       <c r="D699" s="22" t="n">
         <f aca="false">D694*D698/1000</f>
-        <v>10.5297921189288</v>
+        <v>10.5297921189287</v>
       </c>
       <c r="E699" s="22" t="n">
         <f aca="false">E694*E698/1000</f>
@@ -70921,7 +70921,7 @@
       </c>
       <c r="D700" s="21" t="n">
         <f aca="false">D699*fx</f>
-        <v>70.7602030392013</v>
+        <v>70.7602030392012</v>
       </c>
       <c r="E700" s="21" t="n">
         <f aca="false">E699*fx</f>
@@ -70969,7 +70969,7 @@
       </c>
       <c r="D702" s="16" t="n">
         <f aca="false">a26_ai/D700</f>
-        <v>0.247531793970354</v>
+        <v>0.247531793970355</v>
       </c>
       <c r="K702" s="7" t="s">
         <v>510</v>
@@ -71008,7 +71008,7 @@
       </c>
       <c r="D704" s="16" t="n">
         <f aca="false">$D$702*D703</f>
-        <v>0.247531793970354</v>
+        <v>0.247531793970355</v>
       </c>
       <c r="E704" s="16" t="n">
         <f aca="false">$D$702*E703</f>
@@ -71016,7 +71016,7 @@
       </c>
       <c r="F704" s="16" t="n">
         <f aca="false">$D$702*F703</f>
-        <v>0.198025435176283</v>
+        <v>0.198025435176284</v>
       </c>
       <c r="G704" s="16" t="n">
         <f aca="false">$D$702*G703</f>
@@ -71036,15 +71036,15 @@
       </c>
       <c r="E705" s="21" t="n">
         <f aca="false">E700*E704*E701</f>
-        <v>42.521485414958</v>
+        <v>42.5214854149581</v>
       </c>
       <c r="F705" s="21" t="n">
         <f aca="false">F700*F704*F701</f>
-        <v>53.9704970084141</v>
+        <v>53.9704970084142</v>
       </c>
       <c r="G705" s="21" t="n">
         <f aca="false">G700*G704*G701</f>
-        <v>61.8503592901069</v>
+        <v>61.850359290107</v>
       </c>
     </row>
     <row r="706" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -71152,11 +71152,11 @@
       </c>
       <c r="F710" s="21" t="n">
         <f aca="false">MIN(F705,F708-F709)</f>
-        <v>53.9704970084141</v>
+        <v>53.9704970084142</v>
       </c>
       <c r="G710" s="21" t="n">
         <f aca="false">MIN(G705,G708-G709)</f>
-        <v>61.8503592901069</v>
+        <v>61.850359290107</v>
       </c>
       <c r="K710" s="3" t="s">
         <v>519</v>
@@ -71200,11 +71200,11 @@
       </c>
       <c r="F712" s="21" t="n">
         <f aca="false">F710+F709</f>
-        <v>64.5810970084141</v>
+        <v>64.5810970084142</v>
       </c>
       <c r="G712" s="21" t="n">
         <f aca="false">G710+G709</f>
-        <v>72.4609592901069</v>
+        <v>72.460959290107</v>
       </c>
       <c r="H712" s="23" t="n">
         <f aca="false">G712*(1+H713)</f>
@@ -71212,11 +71212,11 @@
       </c>
       <c r="I712" s="23" t="n">
         <f aca="false">H712*(1+I713)</f>
-        <v>86.2423476187718</v>
+        <v>86.2423476187719</v>
       </c>
       <c r="J712" s="23" t="n">
         <f aca="false">I712*(1+J713)</f>
-        <v>91.4168884758982</v>
+        <v>91.4168884758983</v>
       </c>
       <c r="K712" s="7" t="s">
         <v>521</v>
@@ -71239,7 +71239,7 @@
       </c>
       <c r="F713" s="16" t="n">
         <f aca="false">F712/E712-1</f>
-        <v>0.350667730682813</v>
+        <v>0.350667730682815</v>
       </c>
       <c r="G713" s="16" t="n">
         <f aca="false">G712/F712-1</f>
@@ -71303,11 +71303,11 @@
       </c>
       <c r="F715" s="16" t="n">
         <f aca="false">(F705+F709)/F708</f>
-        <v>0.986312346288996</v>
+        <v>0.986312346288997</v>
       </c>
       <c r="G715" s="16" t="n">
         <f aca="false">(G705+G709)/G708</f>
-        <v>0.913580873028148</v>
+        <v>0.913580873028149</v>
       </c>
       <c r="K715" s="3" t="s">
         <v>525</v>
@@ -71322,7 +71322,7 @@
       </c>
       <c r="D716" s="20" t="n">
         <f aca="false">D710/fx/D694*1000</f>
-        <v>111.389307286659</v>
+        <v>111.38930728666</v>
       </c>
       <c r="E716" s="20" t="n">
         <f aca="false">E710/fx/E694*1000</f>
@@ -71334,7 +71334,7 @@
       </c>
       <c r="G716" s="20" t="n">
         <f aca="false">G710/fx/G694*1000</f>
-        <v>153.04519523496</v>
+        <v>153.045195234961</v>
       </c>
     </row>
     <row r="717" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -71520,7 +71520,7 @@
       </c>
       <c r="F724" s="21" t="n">
         <f aca="false">F720-F723</f>
-        <v>19.6292156264786</v>
+        <v>19.6292156264787</v>
       </c>
       <c r="G724" s="21" t="n">
         <f aca="false">G720-G723</f>
@@ -71611,11 +71611,11 @@
       </c>
       <c r="I727" s="23" t="n">
         <f aca="false">I712*I732</f>
-        <v>22.7517562493559</v>
+        <v>22.751756249356</v>
       </c>
       <c r="J727" s="23" t="n">
         <f aca="false">J712*J732</f>
-        <v>24.4489205143475</v>
+        <v>24.4489205143476</v>
       </c>
     </row>
     <row r="728" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -71746,11 +71746,11 @@
       </c>
       <c r="F731" s="16" t="n">
         <f aca="false">F730/E730-1</f>
-        <v>0.373956550945176</v>
+        <v>0.373956550945178</v>
       </c>
       <c r="G731" s="16" t="n">
         <f aca="false">G730/F730-1</f>
-        <v>0.103562510492867</v>
+        <v>0.103562510492866</v>
       </c>
       <c r="H731" s="24" t="n">
         <f aca="false">H730/G730-1</f>
@@ -71758,7 +71758,7 @@
       </c>
       <c r="I731" s="24" t="n">
         <f aca="false">I730/H730-1</f>
-        <v>0.0957588887280154</v>
+        <v>0.0957588887280156</v>
       </c>
       <c r="J731" s="24" t="n">
         <f aca="false">J730/I730-1</f>
@@ -71859,7 +71859,7 @@
       </c>
       <c r="D738" s="22" t="n">
         <f aca="false">itc_26*1</f>
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="E738" s="22" t="n">
         <f aca="false">itc_27*1*1</f>
@@ -72027,7 +72027,7 @@
       </c>
       <c r="D745" s="22" t="n">
         <f aca="false">D740*D744/1000</f>
-        <v>10.5297921189288</v>
+        <v>10.5297921189287</v>
       </c>
       <c r="E745" s="22" t="n">
         <f aca="false">E740*E744/1000</f>
@@ -72051,7 +72051,7 @@
       </c>
       <c r="D746" s="21" t="n">
         <f aca="false">D745*fx</f>
-        <v>70.7602030392013</v>
+        <v>70.7602030392012</v>
       </c>
       <c r="E746" s="21" t="n">
         <f aca="false">E745*fx</f>
@@ -72099,7 +72099,7 @@
       </c>
       <c r="D748" s="16" t="n">
         <f aca="false">a26_ai/D746</f>
-        <v>0.247531793970354</v>
+        <v>0.247531793970355</v>
       </c>
       <c r="K748" s="7" t="s">
         <v>510</v>
@@ -72138,7 +72138,7 @@
       </c>
       <c r="D750" s="16" t="n">
         <f aca="false">$D$748*D749</f>
-        <v>0.247531793970354</v>
+        <v>0.247531793970355</v>
       </c>
       <c r="E750" s="16" t="n">
         <f aca="false">$D$748*E749</f>
@@ -72146,7 +72146,7 @@
       </c>
       <c r="F750" s="16" t="n">
         <f aca="false">$D$748*F749</f>
-        <v>0.198025435176283</v>
+        <v>0.198025435176284</v>
       </c>
       <c r="G750" s="16" t="n">
         <f aca="false">$D$748*G749</f>
@@ -72166,15 +72166,15 @@
       </c>
       <c r="E751" s="21" t="n">
         <f aca="false">E746*E750*E747</f>
-        <v>42.521485414958</v>
+        <v>42.5214854149581</v>
       </c>
       <c r="F751" s="21" t="n">
         <f aca="false">F746*F750*F747</f>
-        <v>53.9704970084141</v>
+        <v>53.9704970084142</v>
       </c>
       <c r="G751" s="21" t="n">
         <f aca="false">G746*G750*G747</f>
-        <v>61.8503592901069</v>
+        <v>61.850359290107</v>
       </c>
     </row>
     <row r="752" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -72282,11 +72282,11 @@
       </c>
       <c r="F756" s="21" t="n">
         <f aca="false">MIN(F751,F754-F755)</f>
-        <v>53.9704970084141</v>
+        <v>53.9704970084142</v>
       </c>
       <c r="G756" s="21" t="n">
         <f aca="false">MIN(G751,G754-G755)</f>
-        <v>61.8503592901069</v>
+        <v>61.850359290107</v>
       </c>
       <c r="K756" s="3" t="s">
         <v>519</v>
@@ -72330,11 +72330,11 @@
       </c>
       <c r="F758" s="21" t="n">
         <f aca="false">F756+F755</f>
-        <v>64.5810970084141</v>
+        <v>64.5810970084142</v>
       </c>
       <c r="G758" s="21" t="n">
         <f aca="false">G756+G755</f>
-        <v>72.4609592901069</v>
+        <v>72.460959290107</v>
       </c>
       <c r="H758" s="23" t="n">
         <f aca="false">G758*(1+H759)</f>
@@ -72342,11 +72342,11 @@
       </c>
       <c r="I758" s="23" t="n">
         <f aca="false">H758*(1+I759)</f>
-        <v>86.2423476187718</v>
+        <v>86.2423476187719</v>
       </c>
       <c r="J758" s="23" t="n">
         <f aca="false">I758*(1+J759)</f>
-        <v>91.4168884758982</v>
+        <v>91.4168884758983</v>
       </c>
       <c r="K758" s="7" t="s">
         <v>521</v>
@@ -72369,7 +72369,7 @@
       </c>
       <c r="F759" s="16" t="n">
         <f aca="false">F758/E758-1</f>
-        <v>0.350667730682813</v>
+        <v>0.350667730682815</v>
       </c>
       <c r="G759" s="16" t="n">
         <f aca="false">G758/F758-1</f>
@@ -72433,11 +72433,11 @@
       </c>
       <c r="F761" s="16" t="n">
         <f aca="false">(F751+F755)/F754</f>
-        <v>0.986312346288996</v>
+        <v>0.986312346288997</v>
       </c>
       <c r="G761" s="16" t="n">
         <f aca="false">(G751+G755)/G754</f>
-        <v>0.913580873028148</v>
+        <v>0.913580873028149</v>
       </c>
       <c r="K761" s="3" t="s">
         <v>525</v>
@@ -72452,7 +72452,7 @@
       </c>
       <c r="D762" s="20" t="n">
         <f aca="false">D756/fx/D740*1000</f>
-        <v>111.389307286659</v>
+        <v>111.38930728666</v>
       </c>
       <c r="E762" s="20" t="n">
         <f aca="false">E756/fx/E740*1000</f>
@@ -72464,7 +72464,7 @@
       </c>
       <c r="G762" s="20" t="n">
         <f aca="false">G756/fx/G740*1000</f>
-        <v>153.04519523496</v>
+        <v>153.045195234961</v>
       </c>
     </row>
     <row r="763" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -72729,7 +72729,7 @@
       </c>
       <c r="F773" s="21" t="n">
         <f aca="false">(F770+F772)*nir_f</f>
-        <v>18.0920907604828</v>
+        <v>18.0920907604829</v>
       </c>
       <c r="G773" s="21" t="n">
         <f aca="false">(G770+G772)*nir_f</f>
@@ -72737,7 +72737,7 @@
       </c>
       <c r="H773" s="23" t="n">
         <f aca="false">H758*H778</f>
-        <v>21.9229820879516</v>
+        <v>21.9229820879517</v>
       </c>
       <c r="I773" s="23" t="n">
         <f aca="false">I758*I778</f>
@@ -72745,7 +72745,7 @@
       </c>
       <c r="J773" s="23" t="n">
         <f aca="false">J758*J778</f>
-        <v>24.4489205143475</v>
+        <v>24.4489205143476</v>
       </c>
     </row>
     <row r="774" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -72844,7 +72844,7 @@
       </c>
       <c r="G776" s="22" t="n">
         <f aca="false">G773/G775</f>
-        <v>20.5314645433714</v>
+        <v>20.5314645433715</v>
       </c>
       <c r="H776" s="28" t="n">
         <f aca="false">H773/H775</f>
@@ -72876,7 +72876,7 @@
       </c>
       <c r="F777" s="16" t="n">
         <f aca="false">F776/E776-1</f>
-        <v>0.402024127405182</v>
+        <v>0.402024127405184</v>
       </c>
       <c r="G777" s="16" t="n">
         <f aca="false">G776/F776-1</f>
@@ -72884,11 +72884,11 @@
       </c>
       <c r="H777" s="24" t="n">
         <f aca="false">H776/G776-1</f>
-        <v>0.0869707839931533</v>
+        <v>0.0869707839931528</v>
       </c>
       <c r="I777" s="24" t="n">
         <f aca="false">I776/H776-1</f>
-        <v>0.0663824092529965</v>
+        <v>0.0663824092529968</v>
       </c>
       <c r="J777" s="24" t="n">
         <f aca="false">J776/I776-1</f>
@@ -72989,7 +72989,7 @@
       </c>
       <c r="D784" s="22" t="n">
         <f aca="false">itc_26*1</f>
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="E784" s="22" t="n">
         <f aca="false">itc_27*1*1</f>
@@ -73157,7 +73157,7 @@
       </c>
       <c r="D791" s="22" t="n">
         <f aca="false">D786*D790/1000</f>
-        <v>10.5297921189288</v>
+        <v>10.5297921189287</v>
       </c>
       <c r="E791" s="22" t="n">
         <f aca="false">E786*E790/1000</f>
@@ -73181,7 +73181,7 @@
       </c>
       <c r="D792" s="21" t="n">
         <f aca="false">D791*fx</f>
-        <v>70.7602030392013</v>
+        <v>70.7602030392012</v>
       </c>
       <c r="E792" s="21" t="n">
         <f aca="false">E791*fx</f>
@@ -73229,7 +73229,7 @@
       </c>
       <c r="D794" s="16" t="n">
         <f aca="false">a26_ai/D792</f>
-        <v>0.247531793970354</v>
+        <v>0.247531793970355</v>
       </c>
       <c r="K794" s="7" t="s">
         <v>510</v>
@@ -73268,7 +73268,7 @@
       </c>
       <c r="D796" s="16" t="n">
         <f aca="false">$D$794*D795</f>
-        <v>0.247531793970354</v>
+        <v>0.247531793970355</v>
       </c>
       <c r="E796" s="16" t="n">
         <f aca="false">$D$794*E795</f>
@@ -73276,7 +73276,7 @@
       </c>
       <c r="F796" s="16" t="n">
         <f aca="false">$D$794*F795</f>
-        <v>0.198025435176283</v>
+        <v>0.198025435176284</v>
       </c>
       <c r="G796" s="16" t="n">
         <f aca="false">$D$794*G795</f>
@@ -73296,15 +73296,15 @@
       </c>
       <c r="E797" s="21" t="n">
         <f aca="false">E792*E796*E793</f>
-        <v>42.521485414958</v>
+        <v>42.5214854149581</v>
       </c>
       <c r="F797" s="21" t="n">
         <f aca="false">F792*F796*F793</f>
-        <v>53.9704970084141</v>
+        <v>53.9704970084142</v>
       </c>
       <c r="G797" s="21" t="n">
         <f aca="false">G792*G796*G793</f>
-        <v>61.8503592901069</v>
+        <v>61.850359290107</v>
       </c>
     </row>
     <row r="798" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -73412,11 +73412,11 @@
       </c>
       <c r="F802" s="21" t="n">
         <f aca="false">MIN(F797,F800-F801)</f>
-        <v>53.9704970084141</v>
+        <v>53.9704970084142</v>
       </c>
       <c r="G802" s="21" t="n">
         <f aca="false">MIN(G797,G800-G801)</f>
-        <v>61.8503592901069</v>
+        <v>61.850359290107</v>
       </c>
       <c r="K802" s="3" t="s">
         <v>519</v>
@@ -73460,11 +73460,11 @@
       </c>
       <c r="F804" s="21" t="n">
         <f aca="false">F802+F801</f>
-        <v>63.5465635084141</v>
+        <v>63.5465635084142</v>
       </c>
       <c r="G804" s="21" t="n">
         <f aca="false">G802+G801</f>
-        <v>70.9476224651069</v>
+        <v>70.947622465107</v>
       </c>
       <c r="H804" s="23" t="n">
         <f aca="false">G804*(1+H805)</f>
@@ -73472,7 +73472,7 @@
       </c>
       <c r="I804" s="23" t="n">
         <f aca="false">H804*(1+I805)</f>
-        <v>84.0135680431227</v>
+        <v>84.0135680431228</v>
       </c>
       <c r="J804" s="23" t="n">
         <f aca="false">I804*(1+J805)</f>
@@ -73499,19 +73499,19 @@
       </c>
       <c r="F805" s="16" t="n">
         <f aca="false">F804/E804-1</f>
-        <v>0.329031198020968</v>
+        <v>0.329031198020969</v>
       </c>
       <c r="G805" s="16" t="n">
         <f aca="false">G804/F804-1</f>
-        <v>0.116466706428788</v>
+        <v>0.116466706428787</v>
       </c>
       <c r="H805" s="24" t="n">
         <f aca="false">$G805+(fade_gA-$G805)*1/3</f>
-        <v>0.0976444709525251</v>
+        <v>0.0976444709525249</v>
       </c>
       <c r="I805" s="24" t="n">
         <f aca="false">$G805+(fade_gA-$G805)*2/3</f>
-        <v>0.0788222354762626</v>
+        <v>0.0788222354762625</v>
       </c>
       <c r="J805" s="24" t="n">
         <f aca="false">$G805+(fade_gA-$G805)*3/3</f>
@@ -73543,7 +73543,7 @@
       </c>
       <c r="G806" s="16" t="n">
         <f aca="false">G802/G804</f>
-        <v>0.871774939611624</v>
+        <v>0.871774939611625</v>
       </c>
     </row>
     <row r="807" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -73563,11 +73563,11 @@
       </c>
       <c r="F807" s="16" t="n">
         <f aca="false">(F797+F801)/F800</f>
-        <v>0.970512472781634</v>
+        <v>0.970512472781636</v>
       </c>
       <c r="G807" s="16" t="n">
         <f aca="false">(G797+G801)/G800</f>
-        <v>0.894500866479602</v>
+        <v>0.894500866479603</v>
       </c>
       <c r="K807" s="3" t="s">
         <v>525</v>
@@ -73582,7 +73582,7 @@
       </c>
       <c r="D808" s="20" t="n">
         <f aca="false">D802/fx/D786*1000</f>
-        <v>111.389307286659</v>
+        <v>111.38930728666</v>
       </c>
       <c r="E808" s="20" t="n">
         <f aca="false">E802/fx/E786*1000</f>
@@ -73594,7 +73594,7 @@
       </c>
       <c r="G808" s="20" t="n">
         <f aca="false">G802/fx/G786*1000</f>
-        <v>153.04519523496</v>
+        <v>153.045195234961</v>
       </c>
     </row>
     <row r="809" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -73970,7 +73970,7 @@
       </c>
       <c r="F822" s="22" t="n">
         <f aca="false">F819/F821</f>
-        <v>17.5955460965734</v>
+        <v>17.5955460965735</v>
       </c>
       <c r="G822" s="22" t="n">
         <f aca="false">G819/G821</f>
@@ -73978,7 +73978,7 @@
       </c>
       <c r="H822" s="28" t="n">
         <f aca="false">H819/H821</f>
-        <v>21.3011249869457</v>
+        <v>21.3011249869458</v>
       </c>
       <c r="I822" s="28" t="n">
         <f aca="false">I819/I821</f>
@@ -74006,7 +74006,7 @@
       </c>
       <c r="F823" s="16" t="n">
         <f aca="false">F822/E822-1</f>
-        <v>0.365753062226712</v>
+        <v>0.365753062226714</v>
       </c>
       <c r="G823" s="16" t="n">
         <f aca="false">G822/F822-1</f>
@@ -74014,15 +74014,15 @@
       </c>
       <c r="H823" s="24" t="n">
         <f aca="false">H822/G822-1</f>
-        <v>0.0950891074005589</v>
+        <v>0.0950891074005587</v>
       </c>
       <c r="I823" s="24" t="n">
         <f aca="false">I822/H822-1</f>
-        <v>0.0763048302706437</v>
+        <v>0.0763048302706435</v>
       </c>
       <c r="J823" s="24" t="n">
         <f aca="false">J822/I822-1</f>
-        <v>0.0575207307048087</v>
+        <v>0.0575207307048089</v>
       </c>
     </row>
     <row r="824" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -74119,7 +74119,7 @@
       </c>
       <c r="D830" s="22" t="n">
         <f aca="false">itc_26*1</f>
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="E830" s="22" t="n">
         <f aca="false">itc_27*1*1</f>
@@ -74287,7 +74287,7 @@
       </c>
       <c r="D837" s="22" t="n">
         <f aca="false">D832*D836/1000</f>
-        <v>10.5297921189288</v>
+        <v>10.5297921189287</v>
       </c>
       <c r="E837" s="22" t="n">
         <f aca="false">E832*E836/1000</f>
@@ -74311,7 +74311,7 @@
       </c>
       <c r="D838" s="21" t="n">
         <f aca="false">D837*fx</f>
-        <v>70.7602030392013</v>
+        <v>70.7602030392012</v>
       </c>
       <c r="E838" s="21" t="n">
         <f aca="false">E837*fx</f>
@@ -74359,7 +74359,7 @@
       </c>
       <c r="D840" s="16" t="n">
         <f aca="false">a26_ai/D838</f>
-        <v>0.247531793970354</v>
+        <v>0.247531793970355</v>
       </c>
       <c r="K840" s="7" t="s">
         <v>510</v>
@@ -74398,7 +74398,7 @@
       </c>
       <c r="D842" s="16" t="n">
         <f aca="false">$D$840*D841</f>
-        <v>0.247531793970354</v>
+        <v>0.247531793970355</v>
       </c>
       <c r="E842" s="16" t="n">
         <f aca="false">$D$840*E841</f>
@@ -74406,7 +74406,7 @@
       </c>
       <c r="F842" s="16" t="n">
         <f aca="false">$D$840*F841</f>
-        <v>0.198025435176283</v>
+        <v>0.198025435176284</v>
       </c>
       <c r="G842" s="16" t="n">
         <f aca="false">$D$840*G841</f>
@@ -74426,15 +74426,15 @@
       </c>
       <c r="E843" s="21" t="n">
         <f aca="false">E838*E842*E839</f>
-        <v>42.521485414958</v>
+        <v>42.5214854149581</v>
       </c>
       <c r="F843" s="21" t="n">
         <f aca="false">F838*F842*F839</f>
-        <v>53.9704970084141</v>
+        <v>53.9704970084142</v>
       </c>
       <c r="G843" s="21" t="n">
         <f aca="false">G838*G842*G839</f>
-        <v>61.8503592901069</v>
+        <v>61.850359290107</v>
       </c>
     </row>
     <row r="844" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -74546,7 +74546,7 @@
       </c>
       <c r="G848" s="21" t="n">
         <f aca="false">MIN(G843,G846-G847)</f>
-        <v>61.8503592901069</v>
+        <v>61.850359290107</v>
       </c>
       <c r="K848" s="3" t="s">
         <v>519</v>
@@ -74594,19 +74594,19 @@
       </c>
       <c r="G850" s="21" t="n">
         <f aca="false">G848+G847</f>
-        <v>74.1334551151069</v>
+        <v>74.133455115107</v>
       </c>
       <c r="H850" s="23" t="n">
         <f aca="false">G850*(1+H851)</f>
-        <v>82.1497711102536</v>
+        <v>82.1497711102537</v>
       </c>
       <c r="I850" s="23" t="n">
         <f aca="false">H850*(1+I851)</f>
-        <v>89.0558387197963</v>
+        <v>89.0558387197964</v>
       </c>
       <c r="J850" s="23" t="n">
         <f aca="false">I850*(1+J851)</f>
-        <v>94.3991890429841</v>
+        <v>94.3991890429842</v>
       </c>
       <c r="K850" s="7" t="s">
         <v>521</v>
@@ -74633,15 +74633,15 @@
       </c>
       <c r="G851" s="16" t="n">
         <f aca="false">G850/F850-1</f>
-        <v>0.132200371938008</v>
+        <v>0.132200371938009</v>
       </c>
       <c r="H851" s="24" t="n">
         <f aca="false">$G851+(fade_gA-$G851)*1/3</f>
-        <v>0.108133581292005</v>
+        <v>0.108133581292006</v>
       </c>
       <c r="I851" s="24" t="n">
         <f aca="false">$G851+(fade_gA-$G851)*2/3</f>
-        <v>0.0840667906460026</v>
+        <v>0.084066790646003</v>
       </c>
       <c r="J851" s="24" t="n">
         <f aca="false">$G851+(fade_gA-$G851)*3/3</f>
@@ -74697,7 +74697,7 @@
       </c>
       <c r="G853" s="16" t="n">
         <f aca="false">(G843+G847)/G846</f>
-        <v>0.934667541089249</v>
+        <v>0.93466754108925</v>
       </c>
       <c r="K853" s="3" t="s">
         <v>525</v>
@@ -74712,7 +74712,7 @@
       </c>
       <c r="D854" s="20" t="n">
         <f aca="false">D848/fx/D832*1000</f>
-        <v>111.389307286659</v>
+        <v>111.38930728666</v>
       </c>
       <c r="E854" s="20" t="n">
         <f aca="false">E848/fx/E832*1000</f>
@@ -74724,7 +74724,7 @@
       </c>
       <c r="G854" s="20" t="n">
         <f aca="false">G848/fx/G832*1000</f>
-        <v>153.04519523496</v>
+        <v>153.045195234961</v>
       </c>
     </row>
     <row r="855" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -75112,7 +75112,7 @@
       </c>
       <c r="I868" s="28" t="n">
         <f aca="false">I865/I867</f>
-        <v>24.1857745054106</v>
+        <v>24.1857745054107</v>
       </c>
       <c r="J868" s="28" t="n">
         <f aca="false">J865/J867</f>
@@ -75140,7 +75140,7 @@
       </c>
       <c r="G869" s="16" t="n">
         <f aca="false">G868/F868-1</f>
-        <v>0.117987078160025</v>
+        <v>0.117987078160026</v>
       </c>
       <c r="H869" s="24" t="n">
         <f aca="false">H868/G868-1</f>
@@ -75148,11 +75148,11 @@
       </c>
       <c r="I869" s="24" t="n">
         <f aca="false">I868/H868-1</f>
-        <v>0.0867571987581293</v>
+        <v>0.0867571987581295</v>
       </c>
       <c r="J869" s="24" t="n">
         <f aca="false">J868/I868-1</f>
-        <v>0.0626241672032295</v>
+        <v>0.0626241672032293</v>
       </c>
     </row>
     <row r="870" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -75249,7 +75249,7 @@
       </c>
       <c r="D876" s="22" t="n">
         <f aca="false">itc_26*1</f>
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="E876" s="22" t="n">
         <f aca="false">itc_27*1*1</f>
@@ -75417,7 +75417,7 @@
       </c>
       <c r="D883" s="22" t="n">
         <f aca="false">D878*D882/1000</f>
-        <v>10.5297921189288</v>
+        <v>10.5297921189287</v>
       </c>
       <c r="E883" s="22" t="n">
         <f aca="false">E878*E882/1000</f>
@@ -75441,7 +75441,7 @@
       </c>
       <c r="D884" s="21" t="n">
         <f aca="false">D883*fx</f>
-        <v>70.7602030392013</v>
+        <v>70.7602030392012</v>
       </c>
       <c r="E884" s="21" t="n">
         <f aca="false">E883*fx</f>
@@ -75489,7 +75489,7 @@
       </c>
       <c r="D886" s="16" t="n">
         <f aca="false">a26_ai/D884</f>
-        <v>0.247531793970354</v>
+        <v>0.247531793970355</v>
       </c>
       <c r="K886" s="7" t="s">
         <v>510</v>
@@ -75528,7 +75528,7 @@
       </c>
       <c r="D888" s="16" t="n">
         <f aca="false">$D$886*D887</f>
-        <v>0.247531793970354</v>
+        <v>0.247531793970355</v>
       </c>
       <c r="E888" s="16" t="n">
         <f aca="false">$D$886*E887</f>
@@ -75536,7 +75536,7 @@
       </c>
       <c r="F888" s="16" t="n">
         <f aca="false">$D$886*F887</f>
-        <v>0.198025435176283</v>
+        <v>0.198025435176284</v>
       </c>
       <c r="G888" s="16" t="n">
         <f aca="false">$D$886*G887</f>
@@ -75556,15 +75556,15 @@
       </c>
       <c r="E889" s="21" t="n">
         <f aca="false">E884*E888*E885</f>
-        <v>42.521485414958</v>
+        <v>42.5214854149581</v>
       </c>
       <c r="F889" s="21" t="n">
         <f aca="false">F884*F888*F885</f>
-        <v>53.9704970084141</v>
+        <v>53.9704970084142</v>
       </c>
       <c r="G889" s="21" t="n">
         <f aca="false">G884*G888*G885</f>
-        <v>61.8503592901069</v>
+        <v>61.850359290107</v>
       </c>
     </row>
     <row r="890" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -75672,11 +75672,11 @@
       </c>
       <c r="F894" s="21" t="n">
         <f aca="false">MIN(F889,F892-F893)</f>
-        <v>53.9704970084141</v>
+        <v>53.9704970084142</v>
       </c>
       <c r="G894" s="21" t="n">
         <f aca="false">MIN(G889,G892-G893)</f>
-        <v>61.8503592901069</v>
+        <v>61.850359290107</v>
       </c>
       <c r="K894" s="3" t="s">
         <v>519</v>
@@ -75720,11 +75720,11 @@
       </c>
       <c r="F896" s="21" t="n">
         <f aca="false">F894+F893</f>
-        <v>64.5810970084141</v>
+        <v>64.5810970084142</v>
       </c>
       <c r="G896" s="21" t="n">
         <f aca="false">G894+G893</f>
-        <v>72.4609592901069</v>
+        <v>72.460959290107</v>
       </c>
       <c r="H896" s="23" t="n">
         <f aca="false">G896*(1+H897)</f>
@@ -75732,11 +75732,11 @@
       </c>
       <c r="I896" s="23" t="n">
         <f aca="false">H896*(1+I897)</f>
-        <v>86.2423476187718</v>
+        <v>86.2423476187719</v>
       </c>
       <c r="J896" s="23" t="n">
         <f aca="false">I896*(1+J897)</f>
-        <v>91.4168884758982</v>
+        <v>91.4168884758983</v>
       </c>
       <c r="K896" s="7" t="s">
         <v>521</v>
@@ -75759,7 +75759,7 @@
       </c>
       <c r="F897" s="16" t="n">
         <f aca="false">F896/E896-1</f>
-        <v>0.350667730682813</v>
+        <v>0.350667730682815</v>
       </c>
       <c r="G897" s="16" t="n">
         <f aca="false">G896/F896-1</f>
@@ -75823,11 +75823,11 @@
       </c>
       <c r="F899" s="16" t="n">
         <f aca="false">(F889+F893)/F892</f>
-        <v>0.986312346288996</v>
+        <v>0.986312346288997</v>
       </c>
       <c r="G899" s="16" t="n">
         <f aca="false">(G889+G893)/G892</f>
-        <v>0.913580873028148</v>
+        <v>0.913580873028149</v>
       </c>
       <c r="K899" s="3" t="s">
         <v>525</v>
@@ -75842,7 +75842,7 @@
       </c>
       <c r="D900" s="20" t="n">
         <f aca="false">D894/fx/D878*1000</f>
-        <v>111.389307286659</v>
+        <v>111.38930728666</v>
       </c>
       <c r="E900" s="20" t="n">
         <f aca="false">E894/fx/E878*1000</f>
@@ -75854,7 +75854,7 @@
       </c>
       <c r="G900" s="20" t="n">
         <f aca="false">G894/fx/G878*1000</f>
-        <v>153.04519523496</v>
+        <v>153.045195234961</v>
       </c>
     </row>
     <row r="901" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -75981,7 +75981,7 @@
       </c>
       <c r="F906" s="21" t="n">
         <f aca="false">E906*(1+MAX(0,phi_hi*F897))</f>
-        <v>4.1971169070314</v>
+        <v>4.19711690703141</v>
       </c>
       <c r="G906" s="21" t="n">
         <f aca="false">F906*(1+MAX(0,phi_hi*G897))</f>
@@ -76012,7 +76012,7 @@
       </c>
       <c r="F907" s="21" t="n">
         <f aca="false">F906+0*F896</f>
-        <v>4.1971169070314</v>
+        <v>4.19711690703141</v>
       </c>
       <c r="G907" s="21" t="n">
         <f aca="false">G906+0*G896</f>
@@ -76135,7 +76135,7 @@
       </c>
       <c r="J911" s="23" t="n">
         <f aca="false">J896*J916</f>
-        <v>24.4489205143475</v>
+        <v>24.4489205143476</v>
       </c>
     </row>
     <row r="912" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -76230,7 +76230,7 @@
       </c>
       <c r="F914" s="22" t="n">
         <f aca="false">F911/F913</f>
-        <v>16.8511961429311</v>
+        <v>16.8511961429312</v>
       </c>
       <c r="G914" s="22" t="n">
         <f aca="false">G911/G913</f>
@@ -76266,15 +76266,15 @@
       </c>
       <c r="F915" s="16" t="n">
         <f aca="false">F914/E914-1</f>
-        <v>0.363722367451052</v>
+        <v>0.363722367451054</v>
       </c>
       <c r="G915" s="16" t="n">
         <f aca="false">G914/F914-1</f>
-        <v>0.100646914701922</v>
+        <v>0.100646914701921</v>
       </c>
       <c r="H915" s="24" t="n">
         <f aca="false">H914/G914-1</f>
-        <v>0.124708371546254</v>
+        <v>0.124708371546253</v>
       </c>
       <c r="I915" s="24" t="n">
         <f aca="false">I914/H914-1</f>
@@ -76282,7 +76282,7 @@
       </c>
       <c r="J915" s="24" t="n">
         <f aca="false">J914/I914-1</f>
-        <v>0.0815726130290966</v>
+        <v>0.0815726130290964</v>
       </c>
     </row>
     <row r="916" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/victory_giant/dist/20261025_勝宏科技模型_v0.1.1.xlsx
+++ b/victory_giant/dist/20261025_勝宏科技模型_v0.1.1.xlsx
@@ -6213,26 +6213,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台積電模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">tsmc/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台積電個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -6412,26 +6412,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台積電模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">tsmc/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台積電個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -6533,26 +6533,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台積電模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">tsmc/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台積電個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -6654,26 +6654,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台積電模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">tsmc/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台積電個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -6775,26 +6775,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台積電模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">tsmc/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台積電個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -6896,26 +6896,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台積電模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">tsmc/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台積電個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>

--- a/victory_giant/dist/20261025_勝宏科技模型_v0.1.1.xlsx
+++ b/victory_giant/dist/20261025_勝宏科技模型_v0.1.1.xlsx
@@ -17628,26 +17628,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">emc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台光電模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.2.1.xlsx</t>
+      <t xml:space="preserve">emc/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台光電個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -18021,26 +18021,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">emc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台光電模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.2.1.xlsx</t>
+      <t xml:space="preserve">emc/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台光電個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.3.xlsx</t>
     </r>
     <r>
       <rPr>
